--- a/output/env_plan_sales_list_hokkaido_tohoku.xlsx
+++ b/output/env_plan_sales_list_hokkaido_tohoku.xlsx
@@ -11,10 +11,12 @@
     <sheet name="05_更新メモ" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="06_町村改訂時期_20260825" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="07_提出仕様_文字コード" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_改定時期調査_20260825b" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_R9満了候補'!$A$2:$K$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_R9満了候補'!$A$2:$K$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_提出仕様_文字コード'!$A$2:$D$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_改定時期調査_20260825b'!$A$2:$K$28</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -173,7 +175,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -249,11 +251,43 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,6 +346,8 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -621,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1111,6 +1147,50 @@
       <c r="D25" s="4" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>構成</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>08_改定時期調査_20260825b</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>義務団体・主要市の未確認先を優先に計画期間を調査した結果。終期を特定できた11件、計画名・策定年のみ9件、計画そのものを確認できず3件</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>終期を特定できたものだけを確認済にし、推測では埋めていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25 第2回の更新</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>R9年度末満了の新規該当先は出なかった。代わりに令和8年度末満了（一関市＝今年度が改定年度）と満了済・満了期（福島市・江別市）の3件を発見</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>08_改定時期調査_20260825b を参照</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1152,16 +1232,6 @@
           <t>① 令和9年度末で計画期間満了となる先 ｜ 令和9年度当初予算が主戦場</t>
         </is>
       </c>
-      <c r="B1" s="26" t="n"/>
-      <c r="C1" s="26" t="n"/>
-      <c r="D1" s="26" t="n"/>
-      <c r="E1" s="26" t="n"/>
-      <c r="F1" s="26" t="n"/>
-      <c r="G1" s="26" t="n"/>
-      <c r="H1" s="26" t="n"/>
-      <c r="I1" s="26" t="n"/>
-      <c r="J1" s="26" t="n"/>
-      <c r="K1" s="26" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
@@ -1226,16 +1296,16 @@
           <t>■ 確認済：令和9年度末で計画期間満了（＝令和9年度に改定業務、令和9年度当初予算が主戦場）</t>
         </is>
       </c>
-      <c r="B3" s="29" t="n"/>
-      <c r="C3" s="29" t="n"/>
-      <c r="D3" s="29" t="n"/>
-      <c r="E3" s="29" t="n"/>
-      <c r="F3" s="29" t="n"/>
-      <c r="G3" s="29" t="n"/>
-      <c r="H3" s="29" t="n"/>
-      <c r="I3" s="29" t="n"/>
-      <c r="J3" s="29" t="n"/>
-      <c r="K3" s="29" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="36" t="n"/>
+      <c r="D3" s="36" t="n"/>
+      <c r="E3" s="36" t="n"/>
+      <c r="F3" s="36" t="n"/>
+      <c r="G3" s="36" t="n"/>
+      <c r="H3" s="36" t="n"/>
+      <c r="I3" s="36" t="n"/>
+      <c r="J3" s="36" t="n"/>
+      <c r="K3" s="37" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
@@ -1471,31 +1541,31 @@
           <t>■ 期間満了済・改定進行中（別の入り方をする先）</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="29" t="n"/>
-      <c r="K8" s="29" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n"/>
+      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="37" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>◆別扱い</t>
+          <t>◇今年度満了</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>芽室町</t>
+          <t>一関市</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
@@ -1505,12 +1575,12 @@
       </c>
       <c r="E9" s="31" t="inlineStr">
         <is>
-          <t>クリーンめむろ環境基本計画</t>
+          <t>一関市環境基本計画</t>
         </is>
       </c>
       <c r="F9" s="31" t="inlineStr">
         <is>
-          <t>令和8年度(2026) 策定手続中</t>
+          <t>平成29年度〜令和8年度（10年間）</t>
         </is>
       </c>
       <c r="G9" s="31" t="inlineStr">
@@ -1520,29 +1590,29 @@
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>令和8年度の町民参加予定に環境審議会・パブリックコメント・策定予定が掲げられており、まさに策定手続の最中。終期を見るだけでは拾えないが、当年度に動いている数少ない案件</t>
+          <t>令和8年度末で満了＝次期計画は令和9年度開始。改定業務は今年度に実施されるはずで、R9満了先より1年早い。今年度に動いている数少ない案件</t>
         </is>
       </c>
       <c r="I9" s="31" t="inlineStr">
         <is>
-          <t>最優先。今すぐ接触し、既発注か自前策定か、支援できる範囲が残っているかを確認する</t>
+          <t>直ちに接触。既発注か自前策定か、支援できる範囲が残っているかを確認する</t>
         </is>
       </c>
       <c r="J9" s="31" t="inlineStr">
         <is>
-          <t>①既発注・自前策定・支援範囲の確認 ②審議会・パブコメ工程に合わせた短期支援メニュー ③素案レビュー・アンケート二次分析の提案</t>
+          <t>①既発注・自前策定・支援範囲の確認 ②発注済みなら範囲外の二次分析・素案レビュー・財源対応表 ③未発注なら補正での短期策定支援</t>
         </is>
       </c>
       <c r="K9" s="31" t="inlineStr">
         <is>
-          <t>芽室町 令和8年度町民参加予定 https://www.memuro.net/administration/sanka/yotei/R8.html（06_町村改訂時期_20260825 行164）</t>
+          <t>一関市 生活環境課 環境基本計画ページ。市の地球温暖化対策地域推進計画は令和5年度〜令和12年度</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="30" t="inlineStr">
         <is>
-          <t>◆別扱い</t>
+          <t>◇満了期</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
@@ -1552,7 +1622,7 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>津別町</t>
+          <t>江別市</t>
         </is>
       </c>
       <c r="D10" s="30" t="inlineStr">
@@ -1562,12 +1632,12 @@
       </c>
       <c r="E10" s="30" t="inlineStr">
         <is>
-          <t>津別町環境基本計画</t>
+          <t>えべつアジェンダ21―江別市環境管理計画―</t>
         </is>
       </c>
       <c r="F10" s="30" t="inlineStr">
         <is>
-          <t>平成26年度〜令和5年度（10年間・満了済）</t>
+          <t>平成7年度〜（計画期間30年）／後期推進計画は平成26年度〜令和5年度で終了</t>
         </is>
       </c>
       <c r="G10" s="30" t="inlineStr">
@@ -1577,22 +1647,22 @@
       </c>
       <c r="H10" s="30" t="inlineStr">
         <is>
-          <t>令和5年度末で満了済。令和6年度に検証と今後の課題の協議を行っている一方、後継計画の策定状況は未確認。満了したまま次期が立ち上がっていない可能性がある</t>
+          <t>平成7年度に30年計画として策定され終期が到来。後期推進計画も令和5年度で終了しており、後継計画の状況が確認できていない。満了したまま次期が立ち上がっていない可能性がある</t>
         </is>
       </c>
       <c r="I10" s="30" t="inlineStr">
         <is>
-          <t>後継計画の有無を早急に確認する。未策定なら令和8年度補正または令和9年度当初での策定を提案できる</t>
+          <t>後継計画の有無を早急に確認する。未策定なら令和9年度当初での策定提案</t>
         </is>
       </c>
       <c r="J10" s="30" t="inlineStr">
         <is>
-          <t>①後継計画の策定状況の確認 ②満了後の空白期間のリスク整理 ③町村向けの軽量な策定メニューと概算見積</t>
+          <t>①後継計画の策定状況の確認 ②30年計画から現行の制度環境への組み替え提案 ③国の第六次環境基本計画・2035年度目標との差分表</t>
         </is>
       </c>
       <c r="K10" s="30" t="inlineStr">
         <is>
-          <t>津別町 環境基本計画ページ https://www.town.tsubetsu.hokkaido.jp/soshiki/juminkikaku/14/859.html（06_町村改訂時期_20260825 行125）</t>
+          <t>江別市 環境管理計画・環境管理計画後期推進計画のページ</t>
         </is>
       </c>
     </row>
@@ -1604,27 +1674,27 @@
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>苫小牧市</t>
+          <t>福島市</t>
         </is>
       </c>
       <c r="D11" s="31" t="inlineStr">
         <is>
-          <t>努力義務</t>
+          <t>義務（中核市）</t>
         </is>
       </c>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>苫小牧市第4次環境基本計画〜第1期ゼロカーボン推進計画〜</t>
+          <t>第3次福島市環境基本計画</t>
         </is>
       </c>
       <c r="F11" s="31" t="inlineStr">
         <is>
-          <t>令和5年度〜令和12年度（8年間・計画期間中）</t>
+          <t>令和3年度〜令和7年度（5年間・満了済）</t>
         </is>
       </c>
       <c r="G11" s="31" t="inlineStr">
@@ -1634,22 +1704,22 @@
       </c>
       <c r="H11" s="31" t="inlineStr">
         <is>
-          <t>R9満了ではないが、令和8年度第1回環境審議会で計画改定について諮問済。終期だけを見ると取りこぼす期間中改定案件</t>
+          <t>令和7年度末で満了済。中核市で区域施策編の策定義務があり、5年周期のため次の満了も早く来る。第4次の策定状況が未確認</t>
         </is>
       </c>
       <c r="I11" s="31" t="inlineStr">
         <is>
-          <t>発注・受託範囲を確認。範囲外の二次分析・財源対応表・事業者支援で入る</t>
+          <t>第4次の策定状況を早急に確認する</t>
         </is>
       </c>
       <c r="J11" s="31" t="inlineStr">
         <is>
-          <t>①既委託範囲確認 ②産業・業務部門の重点分野仮説 ③公共施設脱炭素との接続提案</t>
+          <t>①第4次の策定状況の確認 ②発注済みなら範囲外の二次分析・レビュー ③未策定なら満了後の空白のリスク整理</t>
         </is>
       </c>
       <c r="K11" s="31" t="inlineStr">
         <is>
-          <t>苫小牧市公式 環境基本計画ページ https://www.city.tomakomai.hokkaido.jp/shizen/kankyohozen/suishin/kihonkeikaku.html ／環境審議会 https://www.city.tomakomai.hokkaido.jp/shizen/kankyohozen/suishin/shingikai.html</t>
+          <t>福島市 環境基本計画（令和3年2月策定）ページ</t>
         </is>
       </c>
     </row>
@@ -1661,27 +1731,27 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>いわき市</t>
+          <t>芽室町</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
         <is>
-          <t>義務（中核市）</t>
+          <t>努力義務</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
         <is>
-          <t>いわき市環境基本計画（第三次）</t>
+          <t>クリーンめむろ環境基本計画</t>
         </is>
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>令和3年度〜令和12年度（計画期間中）</t>
+          <t>令和8年度(2026) 策定手続中</t>
         </is>
       </c>
       <c r="G12" s="30" t="inlineStr">
@@ -1691,46 +1761,86 @@
       </c>
       <c r="H12" s="30" t="inlineStr">
         <is>
-          <t>計画期間中だが、令和8年に『環境基本計画一部改定業務委託』を公募型プロポーザルで発注している。計画期間の途中でも案件が立つ実例</t>
+          <t>令和8年度の町民参加予定に環境審議会・パブリックコメント・策定予定が掲げられており、まさに策定手続の最中。終期を見るだけでは拾えないが、当年度に動いている数少ない案件</t>
         </is>
       </c>
       <c r="I12" s="30" t="inlineStr">
         <is>
-          <t>改定業務は発注済みのため新規受託は困難。範囲外の支援に絞る</t>
+          <t>最優先。今すぐ接触し、既発注か自前策定か、支援できる範囲が残っているかを確認する</t>
         </is>
       </c>
       <c r="J12" s="30" t="inlineStr">
         <is>
-          <t>既委託範囲の確認。範囲外の二次分析、財源対応表、素案レビューの提案</t>
+          <t>①既発注・自前策定・支援範囲の確認 ②審議会・パブコメ工程に合わせた短期支援メニュー ③素案レビュー・アンケート二次分析の提案</t>
         </is>
       </c>
       <c r="K12" s="30" t="inlineStr">
         <is>
-          <t>いわき市 一部改定版（素案）／公募型プロポーザル公告</t>
+          <t>芽室町 令和8年度町民参加予定 https://www.memuro.net/administration/sanka/yotei/R8.html（06_町村改訂時期_20260825 行164）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>■ 確認済：令和9年度満了に該当しない（次の接触時期をカレンダーに置く先）</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="n"/>
-      <c r="C13" s="29" t="n"/>
-      <c r="D13" s="29" t="n"/>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="29" t="n"/>
-      <c r="K13" s="29" t="n"/>
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>◆別扱い</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>津別町</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>津別町環境基本計画</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>平成26年度〜令和5年度（10年間・満了済）</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>令和5年度末で満了済。令和6年度に検証と今後の課題の協議を行っている一方、後継計画の策定状況は未確認。満了したまま次期が立ち上がっていない可能性がある</t>
+        </is>
+      </c>
+      <c r="I13" s="31" t="inlineStr">
+        <is>
+          <t>後継計画の有無を早急に確認する。未策定なら令和8年度補正または令和9年度当初での策定を提案できる</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>①後継計画の策定状況の確認 ②満了後の空白期間のリスク整理 ③町村向けの軽量な策定メニューと概算見積</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>津別町 環境基本計画ページ https://www.town.tsubetsu.hokkaido.jp/soshiki/juminkikaku/14/859.html（06_町村改訂時期_20260825 行125）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>－非該当</t>
+          <t>◆別扱い</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -1740,22 +1850,22 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>札幌市</t>
+          <t>苫小牧市</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>義務（指定都市）</t>
+          <t>努力義務</t>
         </is>
       </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
-          <t>第2次札幌市環境基本計画</t>
+          <t>苫小牧市第4次環境基本計画〜第1期ゼロカーボン推進計画〜</t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
         <is>
-          <t>平成30年度〜令和12年度</t>
+          <t>令和5年度〜令和12年度（8年間・計画期間中）</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr">
@@ -1765,54 +1875,54 @@
       </c>
       <c r="H14" s="30" t="inlineStr">
         <is>
-          <t>令和12年度満了のため、改定業務は令和12年度・予算は令和12年度当初。接触は令和11年度の予算要求期</t>
+          <t>R9満了ではないが、令和8年度第1回環境審議会で計画改定について諮問済。終期だけを見ると取りこぼす期間中改定案件</t>
         </is>
       </c>
       <c r="I14" s="30" t="inlineStr">
         <is>
-          <t>令和11年度（2029年）夏〜秋</t>
+          <t>発注・受託範囲を確認。範囲外の二次分析・財源対応表・事業者支援で入る</t>
         </is>
       </c>
       <c r="J14" s="30" t="inlineStr">
         <is>
-          <t>中間見直しの規定があれば期間中でも案件化の余地。まず規定の有無を確認する</t>
+          <t>①既委託範囲確認 ②産業・業務部門の重点分野仮説 ③公共施設脱炭素との接続提案</t>
         </is>
       </c>
       <c r="K14" s="30" t="inlineStr">
         <is>
-          <t>札幌市 資料編PDF（2018-2030）</t>
+          <t>苫小牧市公式 環境基本計画ページ https://www.city.tomakomai.hokkaido.jp/shizen/kankyohozen/suishin/kihonkeikaku.html ／環境審議会 https://www.city.tomakomai.hokkaido.jp/shizen/kankyohozen/suishin/shingikai.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>－非該当</t>
+          <t>◆別扱い</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>仙台市</t>
+          <t>いわき市</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>義務（指定都市）</t>
+          <t>義務（中核市）</t>
         </is>
       </c>
       <c r="E15" s="31" t="inlineStr">
         <is>
-          <t>杜の都環境プラン（仙台市環境基本計画）</t>
+          <t>いわき市環境基本計画（第三次）</t>
         </is>
       </c>
       <c r="F15" s="31" t="inlineStr">
         <is>
-          <t>令和3年度〜令和12年度</t>
+          <t>令和3年度〜令和12年度（計画期間中）</t>
         </is>
       </c>
       <c r="G15" s="31" t="inlineStr">
@@ -1822,81 +1932,41 @@
       </c>
       <c r="H15" s="31" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>計画期間中だが、令和8年に『環境基本計画一部改定業務委託』を公募型プロポーザルで発注している。計画期間の途中でも案件が立つ実例</t>
         </is>
       </c>
       <c r="I15" s="31" t="inlineStr">
         <is>
-          <t>令和11年度（2029年）夏〜秋</t>
+          <t>改定業務は発注済みのため新規受託は困難。範囲外の支援に絞る</t>
         </is>
       </c>
       <c r="J15" s="31" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>既委託範囲の確認。範囲外の二次分析、財源対応表、素案レビューの提案</t>
         </is>
       </c>
       <c r="K15" s="31" t="inlineStr">
         <is>
-          <t>仙台市サイト／概要版</t>
+          <t>いわき市 一部改定版（素案）／公募型プロポーザル公告</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>－非該当</t>
-        </is>
-      </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>岩手県</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="inlineStr">
-        <is>
-          <t>盛岡市</t>
-        </is>
-      </c>
-      <c r="D16" s="30" t="inlineStr">
-        <is>
-          <t>義務（中核市）</t>
-        </is>
-      </c>
-      <c r="E16" s="30" t="inlineStr">
-        <is>
-          <t>盛岡市環境基本計画（第三次）</t>
-        </is>
-      </c>
-      <c r="F16" s="30" t="inlineStr">
-        <is>
-          <t>令和3年度〜令和12年度</t>
-        </is>
-      </c>
-      <c r="G16" s="30" t="inlineStr">
-        <is>
-          <t>確認済</t>
-        </is>
-      </c>
-      <c r="H16" s="30" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="I16" s="30" t="inlineStr">
-        <is>
-          <t>令和11年度（2029年）夏〜秋</t>
-        </is>
-      </c>
-      <c r="J16" s="30" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="K16" s="30" t="inlineStr">
-        <is>
-          <t>盛岡市 第三次環境基本計画ページ</t>
-        </is>
-      </c>
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>■ 確認済：令和9年度満了に該当しない（次の接触時期をカレンダーに置く先）</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="37" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
@@ -1906,27 +1976,27 @@
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>八戸市</t>
+          <t>札幌市</t>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>義務（中核市）</t>
+          <t>義務（指定都市）</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
         <is>
-          <t>第3次八戸市環境基本計画</t>
+          <t>第2次札幌市環境基本計画</t>
         </is>
       </c>
       <c r="F17" s="31" t="inlineStr">
         <is>
-          <t>令和5年度〜令和12年度</t>
+          <t>平成30年度〜令和12年度</t>
         </is>
       </c>
       <c r="G17" s="31" t="inlineStr">
@@ -1936,7 +2006,7 @@
       </c>
       <c r="H17" s="31" t="inlineStr">
         <is>
-          <t>同上。令和5年9月策定と新しいため全面改定の余地は小さい</t>
+          <t>令和12年度満了のため、改定業務は令和12年度・予算は令和12年度当初。接触は令和11年度の予算要求期</t>
         </is>
       </c>
       <c r="I17" s="31" t="inlineStr">
@@ -1946,12 +2016,12 @@
       </c>
       <c r="J17" s="31" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>中間見直しの規定があれば期間中でも案件化の余地。まず規定の有無を確認する</t>
         </is>
       </c>
       <c r="K17" s="31" t="inlineStr">
         <is>
-          <t>八戸市 第3次環境基本計画PDF</t>
+          <t>札幌市 資料編PDF（2018-2030）</t>
         </is>
       </c>
     </row>
@@ -1963,32 +2033,32 @@
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>山形県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>山形市</t>
+          <t>仙台市</t>
         </is>
       </c>
       <c r="D18" s="30" t="inlineStr">
         <is>
-          <t>義務（中核市）</t>
+          <t>義務（指定都市）</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
         <is>
-          <t>第4次山形市環境基本計画</t>
+          <t>杜の都環境プラン（仙台市環境基本計画）</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>令和3年度（推定）〜令和12年度</t>
+          <t>令和3年度〜令和12年度</t>
         </is>
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
-          <t>推定</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="H18" s="30" t="inlineStr">
@@ -2003,12 +2073,12 @@
       </c>
       <c r="J18" s="30" t="inlineStr">
         <is>
-          <t>開始年度は推定。終期は令和12年度で確認済</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="K18" s="30" t="inlineStr">
         <is>
-          <t>山形市 第4次環境基本計画ページ</t>
+          <t>仙台市サイト／概要版</t>
         </is>
       </c>
     </row>
@@ -2025,17 +2095,17 @@
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>盛岡市</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>義務（県）</t>
+          <t>義務（中核市）</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>岩手県環境基本計画</t>
+          <t>盛岡市環境基本計画（第三次）</t>
         </is>
       </c>
       <c r="F19" s="31" t="inlineStr">
@@ -2050,7 +2120,7 @@
       </c>
       <c r="H19" s="31" t="inlineStr">
         <is>
-          <t>県計画は令和12年度満了。県内市町村への波及は県の改定後に来る</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="I19" s="31" t="inlineStr">
@@ -2060,487 +2130,230 @@
       </c>
       <c r="J19" s="31" t="inlineStr">
         <is>
-          <t>県は市町村支援の枠組みを持つ場合があるため、期間中でも支援メニューの確認は行う</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="K19" s="31" t="inlineStr">
         <is>
-          <t>岩手県 環境基本計画ページ</t>
+          <t>盛岡市 第三次環境基本計画ページ</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>■ 要確認：終期が特定できておらず、R9満了の可能性を排除できていない主要団体</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="n"/>
-      <c r="C20" s="29" t="n"/>
-      <c r="D20" s="29" t="n"/>
-      <c r="E20" s="29" t="n"/>
-      <c r="F20" s="29" t="n"/>
-      <c r="G20" s="29" t="n"/>
-      <c r="H20" s="29" t="n"/>
-      <c r="I20" s="29" t="n"/>
-      <c r="J20" s="29" t="n"/>
-      <c r="K20" s="29" t="n"/>
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>－非該当</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>八戸市</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>義務（中核市）</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>第3次八戸市環境基本計画</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>令和5年度〜令和12年度</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>同上。令和5年9月策定と新しいため全面改定の余地は小さい</t>
+        </is>
+      </c>
+      <c r="I20" s="30" t="inlineStr">
+        <is>
+          <t>令和11年度（2029年）夏〜秋</t>
+        </is>
+      </c>
+      <c r="J20" s="30" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="K20" s="30" t="inlineStr">
+        <is>
+          <t>八戸市 第3次環境基本計画PDF</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>？要確認</t>
+          <t>－非該当</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>山形市</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>義務（道）</t>
+          <t>義務（中核市）</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>北海道環境基本計画［第3次計画］</t>
+          <t>第4次山形市環境基本計画</t>
         </is>
       </c>
       <c r="F21" s="31" t="inlineStr">
         <is>
-          <t>令和3年度〜（終期未確認）</t>
+          <t>令和3年度（推定）〜令和12年度</t>
         </is>
       </c>
       <c r="G21" s="31" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>推定</t>
         </is>
       </c>
       <c r="H21" s="31" t="inlineStr">
         <is>
-          <t>令和3年3月策定。10年計画なら令和12年度満了だが未確認。道は市町村支援の枠組みを持つ可能性があり、営業ルートとして最優先で当たる価値がある</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="I21" s="31" t="inlineStr">
         <is>
-          <t>終期確認と併せて、道の市町村支援メニューを早期に確認</t>
+          <t>令和11年度（2029年）夏〜秋</t>
         </is>
       </c>
       <c r="J21" s="31" t="inlineStr">
         <is>
-          <t>道の支援メニュー確認が先</t>
+          <t>開始年度は推定。終期は令和12年度で確認済</t>
         </is>
       </c>
       <c r="K21" s="31" t="inlineStr">
         <is>
-          <t>北海道 環境生活部環境政策課</t>
+          <t>山形市 第4次環境基本計画ページ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>？要確認</t>
+          <t>－非該当</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>函館市</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>義務（中核市）</t>
+          <t>義務（県）</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
         <is>
-          <t>函館市環境基本計画［第3次計画］</t>
+          <t>岩手県環境基本計画</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>令和2年度〜（終期未確認）</t>
+          <t>令和3年度〜令和12年度</t>
         </is>
       </c>
       <c r="G22" s="30" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="H22" s="30" t="inlineStr">
         <is>
-          <t>令和2年3月策定。10年なら令和11年度満了だが、8年なら令和9年度満了で該当する。中核市のため確認優先度が高い</t>
+          <t>県計画は令和12年度満了。県内市町村への波及は県の改定後に来る</t>
         </is>
       </c>
       <c r="I22" s="30" t="inlineStr">
         <is>
-          <t>終期を最優先で確認</t>
+          <t>令和11年度（2029年）夏〜秋</t>
         </is>
       </c>
       <c r="J22" s="30" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章</t>
+          <t>県は市町村支援の枠組みを持つ場合があるため、期間中でも支援メニューの確認は行う</t>
         </is>
       </c>
       <c r="K22" s="30" t="inlineStr">
         <is>
-          <t>函館市／EPO北海道</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>？要確認</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>青森県</t>
-        </is>
-      </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>青森市</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>義務（中核市）</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>（未確認）</t>
-        </is>
-      </c>
-      <c r="F23" s="31" t="inlineStr">
-        <is>
-          <t>（未確認）</t>
-        </is>
-      </c>
-      <c r="G23" s="31" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="H23" s="31" t="inlineStr">
-        <is>
-          <t>中核市で義務団体。計画の有無・期間とも未確認のため、確認優先度が高い</t>
-        </is>
-      </c>
-      <c r="I23" s="31" t="inlineStr">
-        <is>
-          <t>終期を最優先で確認</t>
-        </is>
-      </c>
-      <c r="J23" s="31" t="inlineStr">
-        <is>
-          <t>計画PDFの表紙・第1章</t>
-        </is>
-      </c>
-      <c r="K23" s="31" t="inlineStr">
-        <is>
-          <t>青森市サイト</t>
+          <t>岩手県 環境基本計画ページ</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>？要確認</t>
-        </is>
-      </c>
-      <c r="B24" s="30" t="inlineStr">
-        <is>
-          <t>福島県</t>
-        </is>
-      </c>
-      <c r="C24" s="30" t="inlineStr">
-        <is>
-          <t>福島市</t>
-        </is>
-      </c>
-      <c r="D24" s="30" t="inlineStr">
-        <is>
-          <t>義務（中核市）</t>
-        </is>
-      </c>
-      <c r="E24" s="30" t="inlineStr">
-        <is>
-          <t>福島市環境基本計画</t>
-        </is>
-      </c>
-      <c r="F24" s="30" t="inlineStr">
-        <is>
-          <t>令和3年度〜（終期未確認）</t>
-        </is>
-      </c>
-      <c r="G24" s="30" t="inlineStr">
-        <is>
-          <t>一部確認</t>
-        </is>
-      </c>
-      <c r="H24" s="30" t="inlineStr">
-        <is>
-          <t>令和3年2月策定。市の一般廃棄物処理基本計画が令和3〜7年度の5年設定であり、環境基本計画も短期設定なら既に満了または近い可能性がある</t>
-        </is>
-      </c>
-      <c r="I24" s="30" t="inlineStr">
-        <is>
-          <t>終期を最優先で確認</t>
-        </is>
-      </c>
-      <c r="J24" s="30" t="inlineStr">
-        <is>
-          <t>計画PDFの表紙・第1章</t>
-        </is>
-      </c>
-      <c r="K24" s="30" t="inlineStr">
-        <is>
-          <t>福島市サイト</t>
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>確定4件（旭川市・士幌町・秋田市・弘前市）。北海道分は旭川市・士幌町がR9満了確認済で、令和8年度の予算要求期（8〜10月）が接触の山場。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>？要確認</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>青森県</t>
-        </is>
-      </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>青森県</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>義務（県）</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
-        <is>
-          <t>青森県環境総合プラン</t>
-        </is>
-      </c>
-      <c r="F25" s="31" t="inlineStr">
-        <is>
-          <t>令和6年度〜（終期未確認）</t>
-        </is>
-      </c>
-      <c r="G25" s="31" t="inlineStr">
-        <is>
-          <t>一部確認</t>
-        </is>
-      </c>
-      <c r="H25" s="31" t="inlineStr">
-        <is>
-          <t>令和6年3月策定と新しい。県計画が新しい時期は、県内市町村の改定が続く局面に入りやすい</t>
-        </is>
-      </c>
-      <c r="I25" s="31" t="inlineStr">
-        <is>
-          <t>県の市町村支援メニューを確認</t>
-        </is>
-      </c>
-      <c r="J25" s="31" t="inlineStr">
-        <is>
-          <t>県内市町村の策定状況一覧の入手</t>
-        </is>
-      </c>
-      <c r="K25" s="31" t="inlineStr">
-        <is>
-          <t>青森県 環境政策課</t>
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>苫小牧市は第4次計画が令和5年度〜令和12年度のためR9満了ではない。ただし令和8年度に環境審議会へ改定諮問が出ており、期間中改定案件として別管理する。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>？要確認</t>
-        </is>
-      </c>
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t>宮城県</t>
-        </is>
-      </c>
-      <c r="C26" s="30" t="inlineStr">
-        <is>
-          <t>宮城県</t>
-        </is>
-      </c>
-      <c r="D26" s="30" t="inlineStr">
-        <is>
-          <t>義務（県）</t>
-        </is>
-      </c>
-      <c r="E26" s="30" t="inlineStr">
-        <is>
-          <t>（未確認）</t>
-        </is>
-      </c>
-      <c r="F26" s="30" t="inlineStr">
-        <is>
-          <t>（未確認）</t>
-        </is>
-      </c>
-      <c r="G26" s="30" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="H26" s="30" t="inlineStr">
-        <is>
-          <t>県計画の期間・市町村支援を要確認</t>
-        </is>
-      </c>
-      <c r="I26" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="30" t="inlineStr">
-        <is>
-          <t>宮城県 環境政策課</t>
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>『要確認』の団体を該当なしと読まないこと。特に函館市・青森市・福島市は中核市（義務団体）でありながら終期が特定できておらず、確認優先度が最も高い。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>？要確認</t>
-        </is>
-      </c>
-      <c r="B27" s="31" t="inlineStr">
-        <is>
-          <t>秋田県</t>
-        </is>
-      </c>
-      <c r="C27" s="31" t="inlineStr">
-        <is>
-          <t>秋田県</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>義務（県）</t>
-        </is>
-      </c>
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t>（未確認）</t>
-        </is>
-      </c>
-      <c r="F27" s="31" t="inlineStr">
-        <is>
-          <t>（未確認）</t>
-        </is>
-      </c>
-      <c r="G27" s="31" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="H27" s="31" t="inlineStr">
-        <is>
-          <t>県計画の期間・市町村支援を要確認</t>
-        </is>
-      </c>
-      <c r="I27" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K27" s="31" t="inlineStr">
-        <is>
-          <t>秋田県 環境管理課</t>
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>本シートは、02_営業先マスタの終期欄が埋まるたびに行を追加していく運用を前提にしている。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>？要確認</t>
-        </is>
-      </c>
-      <c r="B28" s="30" t="inlineStr">
-        <is>
-          <t>山形県</t>
-        </is>
-      </c>
-      <c r="C28" s="30" t="inlineStr">
-        <is>
-          <t>山形県</t>
-        </is>
-      </c>
-      <c r="D28" s="30" t="inlineStr">
-        <is>
-          <t>義務（県）</t>
-        </is>
-      </c>
-      <c r="E28" s="30" t="inlineStr">
-        <is>
-          <t>第3次山形県環境計画</t>
-        </is>
-      </c>
-      <c r="F28" s="30" t="inlineStr">
-        <is>
-          <t>（未確認）</t>
-        </is>
-      </c>
-      <c r="G28" s="30" t="inlineStr">
-        <is>
-          <t>未確認</t>
-        </is>
-      </c>
-      <c r="H28" s="30" t="inlineStr">
-        <is>
-          <t>県計画の期間・市町村支援を要確認</t>
-        </is>
-      </c>
-      <c r="I28" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K28" s="30" t="inlineStr">
-        <is>
-          <t>山形県 環境企画課</t>
-        </is>
-      </c>
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>■ 2026-08-25 町村調査：計画はあるが期間が確認できていない先（PDFで終期だけ確認する）</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="36" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
+      <c r="F28" s="36" t="n"/>
+      <c r="G28" s="36" t="n"/>
+      <c r="H28" s="36" t="n"/>
+      <c r="I28" s="36" t="n"/>
+      <c r="J28" s="36" t="n"/>
+      <c r="K28" s="37" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
@@ -2550,326 +2363,542 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>上士幌町</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>義務（県）</t>
+          <t>努力義務</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>（未確認）</t>
+          <t>第2次上士幌町環境基本計画</t>
         </is>
       </c>
       <c r="F29" s="31" t="inlineStr">
         <is>
-          <t>（未確認）</t>
+          <t>令和6年度(2024)策定・終期未確認</t>
         </is>
       </c>
       <c r="G29" s="31" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>一部確認</t>
         </is>
       </c>
       <c r="H29" s="31" t="inlineStr">
         <is>
-          <t>県計画の期間・市町村支援を要確認</t>
+          <t>令和6年度策定のため、R9満了ではなくR6策定直後の可能性が高い。ただしHTML上で終期が読めず確定していない</t>
         </is>
       </c>
       <c r="I29" s="31" t="inlineStr">
         <is>
+          <t>PDF本文の計画期間だけ確認する</t>
+        </is>
+      </c>
+      <c r="J29" s="31" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J29" s="31" t="inlineStr">
+      <c r="K29" s="31" t="inlineStr">
+        <is>
+          <t>https://www.kamishihoro.jp/page/00000416（06シート 行160）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>新得町</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>新得町環境基本計画・地球温暖化対策実行計画(区域施策編)・気候変動適応計画</t>
+        </is>
+      </c>
+      <c r="F30" s="30" t="inlineStr">
+        <is>
+          <t>策定済・終期未確認</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H30" s="30" t="inlineStr">
+        <is>
+          <t>環境基本計画と温対・適応計画を一体で掲載している。一体計画のため改定時の業務範囲が広く、単価が伸びやすい</t>
+        </is>
+      </c>
+      <c r="I30" s="30" t="inlineStr">
+        <is>
+          <t>PDF本文で改訂時期・終期を確認する</t>
+        </is>
+      </c>
+      <c r="J30" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K29" s="31" t="inlineStr">
-        <is>
-          <t>福島県 環境共生課</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
+      <c r="K30" s="30" t="inlineStr">
+        <is>
+          <t>https://www.shintoku-town.jp/gyousei/koukai_kouhyou/tyoumin/kankyoukihonkeikaku/（06シート 行162）</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>確定4件（旭川市・士幌町・秋田市・弘前市）。北海道分は旭川市・士幌町がR9満了確認済で、令和8年度の予算要求期（8〜10月）が接触の山場。</t>
-        </is>
-      </c>
-      <c r="B31" s="33" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
-      <c r="E31" s="33" t="n"/>
-      <c r="F31" s="33" t="n"/>
-      <c r="G31" s="33" t="n"/>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="33" t="n"/>
-      <c r="J31" s="33" t="n"/>
-      <c r="K31" s="33" t="n"/>
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>池田町</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>池田町環境基本計画（第3次改訂）</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>令和8年度(2026)改訂・終期未確認</t>
+        </is>
+      </c>
+      <c r="G31" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H31" s="31" t="inlineStr">
+        <is>
+          <t>令和8年度に改訂済み。短期は進捗管理・施策評価・アンケート分析の支援余地</t>
+        </is>
+      </c>
+      <c r="I31" s="31" t="inlineStr">
+        <is>
+          <t>PDF本文で計画期間を確認する</t>
+        </is>
+      </c>
+      <c r="J31" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K31" s="31" t="inlineStr">
+        <is>
+          <t>https://www.town.hokkaido-ikeda.lg.jp/kurashi/kankyo/430.html（06シート 行170）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>苫小牧市は第4次計画が令和5年度〜令和12年度のためR9満了ではない。ただし令和8年度に環境審議会へ改定諮問が出ており、期間中改定案件として別管理する。</t>
-        </is>
-      </c>
-      <c r="B32" s="33" t="n"/>
-      <c r="C32" s="33" t="n"/>
-      <c r="D32" s="33" t="n"/>
-      <c r="E32" s="33" t="n"/>
-      <c r="F32" s="33" t="n"/>
-      <c r="G32" s="33" t="n"/>
-      <c r="H32" s="33" t="n"/>
-      <c r="I32" s="33" t="n"/>
-      <c r="J32" s="33" t="n"/>
-      <c r="K32" s="33" t="n"/>
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>厚岸町</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>第2期厚岸町豊かな環境を守り育てる基本計画</t>
+        </is>
+      </c>
+      <c r="F32" s="30" t="inlineStr">
+        <is>
+          <t>終期未確認</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H32" s="30" t="inlineStr">
+        <is>
+          <t>年次報告が2024年まで公表されており現行性は高い。計画名が『環境基本計画』でないため名称検索から漏れやすい</t>
+        </is>
+      </c>
+      <c r="I32" s="30" t="inlineStr">
+        <is>
+          <t>PDF本文で計画期間だけ確認する</t>
+        </is>
+      </c>
+      <c r="J32" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="30" t="inlineStr">
+        <is>
+          <t>https://www.akkeshi-town.jp/gyosei/seisaku/kankyo/kankyo19/（06シート 行178）</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>『要確認』の団体を該当なしと読まないこと。特に函館市・青森市・福島市は中核市（義務団体）でありながら終期が特定できておらず、確認優先度が最も高い。</t>
-        </is>
-      </c>
-      <c r="B33" s="33" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="33" t="n"/>
-      <c r="G33" s="33" t="n"/>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="33" t="n"/>
-      <c r="J33" s="33" t="n"/>
-      <c r="K33" s="33" t="n"/>
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>鶴居村</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>第2次鶴居村環境基本計画</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>終期未確認</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H33" s="31" t="inlineStr">
+        <is>
+          <t>村公式の計画一覧で第2次計画を確認。HTML上では期間が読めない</t>
+        </is>
+      </c>
+      <c r="I33" s="31" t="inlineStr">
+        <is>
+          <t>PDF本文で計画期間だけ確認する</t>
+        </is>
+      </c>
+      <c r="J33" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="31" t="inlineStr">
+        <is>
+          <t>https://www.vill.tsurui.lg.jp/soshikikarasagasu/kikakuzaiseika/muranokeikaku/804.html（06シート 行182）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>本シートは、02_営業先マスタの終期欄が埋まるたびに行を追加していく運用を前提にしている。</t>
-        </is>
-      </c>
-      <c r="B34" s="33" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
-      <c r="G34" s="33" t="n"/>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="33" t="n"/>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="33" t="n"/>
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>弟子屈町</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="inlineStr">
+        <is>
+          <t>弟子屈町環境基本計画（外部DBで存在確認）</t>
+        </is>
+      </c>
+      <c r="F34" s="30" t="inlineStr">
+        <is>
+          <t>公式終期未確認</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H34" s="30" t="inlineStr">
+        <is>
+          <t>外部データベースで計画名は確認できるが、公式ページ・期間は未確認。外部DB情報だけで終期を埋めないこと</t>
+        </is>
+      </c>
+      <c r="I34" s="30" t="inlineStr">
+        <is>
+          <t>公式PDFの有無と計画期間のみ確認する</t>
+        </is>
+      </c>
+      <c r="J34" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="30" t="inlineStr">
+        <is>
+          <t>外部DB（06シート 行181）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="28" t="inlineStr">
         <is>
-          <t>■ 2026-08-25 町村調査：計画はあるが期間が確認できていない先（PDFで終期だけ確認する）</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="29" t="n"/>
-      <c r="E35" s="29" t="n"/>
-      <c r="F35" s="29" t="n"/>
-      <c r="G35" s="29" t="n"/>
-      <c r="H35" s="29" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="29" t="n"/>
-      <c r="K35" s="29" t="n"/>
+          <t>■ 2026-08-25 追加調査：確認済で令和9年度満了に該当しない先</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n"/>
+      <c r="C35" s="36" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
+      <c r="J35" s="36" t="n"/>
+      <c r="K35" s="37" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="30" t="inlineStr">
         <is>
-          <t>？要確認</t>
+          <t>－非該当</t>
         </is>
       </c>
       <c r="B36" s="30" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>上士幌町</t>
+          <t>青森県</t>
         </is>
       </c>
       <c r="D36" s="30" t="inlineStr">
         <is>
-          <t>努力義務</t>
+          <t>義務（県）</t>
         </is>
       </c>
       <c r="E36" s="30" t="inlineStr">
         <is>
-          <t>第2次上士幌町環境基本計画</t>
+          <t>第6次青森県環境計画（青森県環境総合プラン）</t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>令和6年度(2024)策定・終期未確認</t>
+          <t>令和6年度〜令和10年度（5年間）</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="H36" s="30" t="inlineStr">
         <is>
-          <t>令和6年度策定のため、R9満了ではなくR6策定直後の可能性が高い。ただしHTML上で終期が読めず確定していない</t>
+          <t>令和10年度満了。県計画としては短い5年周期のため、次の改定が比較的早く来る</t>
         </is>
       </c>
       <c r="I36" s="30" t="inlineStr">
         <is>
-          <t>PDF本文の計画期間だけ確認する</t>
+          <t>令和9年度（2027年）夏〜秋に予算要求期の接触</t>
         </is>
       </c>
       <c r="J36" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>県の市町村支援メニューの確認は期間中でも行う</t>
         </is>
       </c>
       <c r="K36" s="30" t="inlineStr">
         <is>
-          <t>https://www.kamishihoro.jp/page/00000416（06シート 行160）</t>
+          <t>青森県 第6次青森県環境計画</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="31" t="inlineStr">
         <is>
-          <t>？要確認</t>
+          <t>－非該当</t>
         </is>
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>新得町</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="D37" s="31" t="inlineStr">
         <is>
-          <t>努力義務</t>
+          <t>義務（県）</t>
         </is>
       </c>
       <c r="E37" s="31" t="inlineStr">
         <is>
-          <t>新得町環境基本計画・地球温暖化対策実行計画(区域施策編)・気候変動適応計画</t>
+          <t>宮城県環境基本計画（第4期）</t>
         </is>
       </c>
       <c r="F37" s="31" t="inlineStr">
         <is>
-          <t>策定済・終期未確認</t>
+          <t>令和3年度〜令和12年度</t>
         </is>
       </c>
       <c r="G37" s="31" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="H37" s="31" t="inlineStr">
         <is>
-          <t>環境基本計画と温対・適応計画を一体で掲載している。一体計画のため改定時の業務範囲が広く、単価が伸びやすい</t>
+          <t>令和12年度満了</t>
         </is>
       </c>
       <c r="I37" s="31" t="inlineStr">
         <is>
-          <t>PDF本文で改訂時期・終期を確認する</t>
+          <t>令和11年度（2029年）夏〜秋</t>
         </is>
       </c>
       <c r="J37" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>県の市町村支援メニューの確認は期間中でも行う</t>
         </is>
       </c>
       <c r="K37" s="31" t="inlineStr">
         <is>
-          <t>https://www.shintoku-town.jp/gyousei/koukai_kouhyou/tyoumin/kankyoukihonkeikaku/（06シート 行162）</t>
+          <t>宮城県公式サイト 環境基本計画（第4期）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="30" t="inlineStr">
         <is>
-          <t>？要確認</t>
+          <t>－非該当</t>
         </is>
       </c>
       <c r="B38" s="30" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>池田町</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="D38" s="30" t="inlineStr">
         <is>
-          <t>努力義務</t>
+          <t>義務（県）</t>
         </is>
       </c>
       <c r="E38" s="30" t="inlineStr">
         <is>
-          <t>池田町環境基本計画（第3次改訂）</t>
+          <t>第4次山形県環境計画</t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
         <is>
-          <t>令和8年度(2026)改訂・終期未確認</t>
+          <t>令和3年度〜令和12年度（10年間）</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="H38" s="30" t="inlineStr">
         <is>
-          <t>令和8年度に改訂済み。短期は進捗管理・施策評価・アンケート分析の支援余地</t>
+          <t>令和12年度満了。従前リストの『第3次』は平成23年度〜令和2年度で終了済のため計画名を訂正した</t>
         </is>
       </c>
       <c r="I38" s="30" t="inlineStr">
         <is>
-          <t>PDF本文で計画期間を確認する</t>
+          <t>令和11年度（2029年）夏〜秋</t>
         </is>
       </c>
       <c r="J38" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>県の市町村支援メニューの確認は期間中でも行う</t>
         </is>
       </c>
       <c r="K38" s="30" t="inlineStr">
         <is>
-          <t>https://www.town.hokkaido-ikeda.lg.jp/kurashi/kankyo/430.html（06シート 行170）</t>
+          <t>山形県 第4次山形県環境計画（令和3年3月策定）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="31" t="inlineStr">
         <is>
-          <t>？要確認</t>
+          <t>－非該当</t>
         </is>
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>厚岸町</t>
+          <t>会津若松市</t>
         </is>
       </c>
       <c r="D39" s="31" t="inlineStr">
@@ -2879,27 +2908,27 @@
       </c>
       <c r="E39" s="31" t="inlineStr">
         <is>
-          <t>第2期厚岸町豊かな環境を守り育てる基本計画</t>
+          <t>会津若松市第3期環境基本計画</t>
         </is>
       </c>
       <c r="F39" s="31" t="inlineStr">
         <is>
-          <t>終期未確認</t>
+          <t>令和6年度〜令和12年度（7年間）</t>
         </is>
       </c>
       <c r="G39" s="31" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="H39" s="31" t="inlineStr">
         <is>
-          <t>年次報告が2024年まで公表されており現行性は高い。計画名が『環境基本計画』でないため名称検索から漏れやすい</t>
+          <t>令和12年度満了</t>
         </is>
       </c>
       <c r="I39" s="31" t="inlineStr">
         <is>
-          <t>PDF本文で計画期間だけ確認する</t>
+          <t>令和11年度（2029年）夏〜秋</t>
         </is>
       </c>
       <c r="J39" s="31" t="inlineStr">
@@ -2909,14 +2938,14 @@
       </c>
       <c r="K39" s="31" t="inlineStr">
         <is>
-          <t>https://www.akkeshi-town.jp/gyosei/seisaku/kankyo/kankyo19/（06シート 行178）</t>
+          <t>会津若松市 第3期環境基本計画（令和6年3月策定）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="30" t="inlineStr">
         <is>
-          <t>？要確認</t>
+          <t>－非該当</t>
         </is>
       </c>
       <c r="B40" s="30" t="inlineStr">
@@ -2926,7 +2955,7 @@
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>鶴居村</t>
+          <t>釧路市</t>
         </is>
       </c>
       <c r="D40" s="30" t="inlineStr">
@@ -2936,109 +2965,925 @@
       </c>
       <c r="E40" s="30" t="inlineStr">
         <is>
-          <t>第2次鶴居村環境基本計画</t>
+          <t>第2次釧路市環境基本計画【改定版】</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>終期未確認</t>
+          <t>令和3年度〜令和12年度</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="H40" s="30" t="inlineStr">
         <is>
-          <t>村公式の計画一覧で第2次計画を確認。HTML上では期間が読めない</t>
+          <t>令和12年度満了。ただし国・北海道の温暖化計画改定を受け、令和6年3月に低炭素社会の形成の目標を一部改定した実績がある</t>
         </is>
       </c>
       <c r="I40" s="30" t="inlineStr">
         <is>
-          <t>PDF本文で計画期間だけ確認する</t>
+          <t>令和11年度（2029年）夏〜秋。ただし部分改定の余地は随時</t>
         </is>
       </c>
       <c r="J40" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>国の2035年度60%・2040年度73%を踏まえた再度の部分改定の提案</t>
         </is>
       </c>
       <c r="K40" s="30" t="inlineStr">
         <is>
-          <t>https://www.vill.tsurui.lg.jp/soshikikarasagasu/kikakuzaiseika/muranokeikaku/804.html（06シート 行182）</t>
+          <t>釧路市 第2次環境基本計画【改定版】</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="31" t="inlineStr">
         <is>
+          <t>－非該当</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>千歳市</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>第3次千歳市環境基本計画</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="inlineStr">
+        <is>
+          <t>令和3年度〜令和12年度</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="H41" s="31" t="inlineStr">
+        <is>
+          <t>令和12年度満了</t>
+        </is>
+      </c>
+      <c r="I41" s="31" t="inlineStr">
+        <is>
+          <t>令和11年度（2029年）夏〜秋</t>
+        </is>
+      </c>
+      <c r="J41" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" s="31" t="inlineStr">
+        <is>
+          <t>千歳市 第3次環境基本計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>－非該当</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>石狩市</t>
+        </is>
+      </c>
+      <c r="D42" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E42" s="30" t="inlineStr">
+        <is>
+          <t>石狩市環境基本計画（第3次）</t>
+        </is>
+      </c>
+      <c r="F42" s="30" t="inlineStr">
+        <is>
+          <t>令和5年度〜（計画期間20年）</t>
+        </is>
+      </c>
+      <c r="G42" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="H42" s="30" t="inlineStr">
+        <is>
+          <t>20年計画のため改定需要は当面ない。中間見直しの規定の有無だけ確認する</t>
+        </is>
+      </c>
+      <c r="I42" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" s="30" t="inlineStr">
+        <is>
+          <t>石狩市 環境基本計画（令和5年3月策定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>－非該当</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>石巻市</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>石巻市環境基本計画（第2次）</t>
+        </is>
+      </c>
+      <c r="F43" s="31" t="inlineStr">
+        <is>
+          <t>令和8年度〜令和17年度（10年間）</t>
+        </is>
+      </c>
+      <c r="G43" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="H43" s="31" t="inlineStr">
+        <is>
+          <t>令和8年3月策定で直後のため新規受託は難しい。進捗管理・アンケート二次分析など周辺支援の余地</t>
+        </is>
+      </c>
+      <c r="I43" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="31" t="inlineStr">
+        <is>
+          <t>石巻市 環境基本計画（令和8年3月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>■ 2026-08-25 追加調査：終期が確認できず、令和9年度満了の可能性を排除できない先</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="n"/>
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="36" t="n"/>
+      <c r="E44" s="36" t="n"/>
+      <c r="F44" s="36" t="n"/>
+      <c r="G44" s="36" t="n"/>
+      <c r="H44" s="36" t="n"/>
+      <c r="I44" s="36" t="n"/>
+      <c r="J44" s="36" t="n"/>
+      <c r="K44" s="37" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
           <t>？要確認</t>
         </is>
       </c>
-      <c r="B41" s="31" t="inlineStr">
+      <c r="B45" s="31" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="C41" s="31" t="inlineStr">
-        <is>
-          <t>弟子屈町</t>
-        </is>
-      </c>
-      <c r="D41" s="31" t="inlineStr">
-        <is>
-          <t>努力義務</t>
-        </is>
-      </c>
-      <c r="E41" s="31" t="inlineStr">
-        <is>
-          <t>弟子屈町環境基本計画（外部DBで存在確認）</t>
-        </is>
-      </c>
-      <c r="F41" s="31" t="inlineStr">
-        <is>
-          <t>公式終期未確認</t>
-        </is>
-      </c>
-      <c r="G41" s="31" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>義務（道）</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>北海道環境基本計画［第3次計画］</t>
+        </is>
+      </c>
+      <c r="F45" s="31" t="inlineStr">
+        <is>
+          <t>令和3年度〜（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G45" s="31" t="inlineStr">
         <is>
           <t>一部確認</t>
         </is>
       </c>
-      <c r="H41" s="31" t="inlineStr">
-        <is>
-          <t>外部データベースで計画名は確認できるが、公式ページ・期間は未確認。外部DB情報だけで終期を埋めないこと</t>
-        </is>
-      </c>
-      <c r="I41" s="31" t="inlineStr">
-        <is>
-          <t>公式PDFの有無と計画期間のみ確認する</t>
-        </is>
-      </c>
-      <c r="J41" s="31" t="inlineStr">
+      <c r="H45" s="31" t="inlineStr">
+        <is>
+          <t>令和3年3月策定。複数回検索したが終期はHTML上で確認できず。道は市町村支援の枠組みを持つ可能性があり、営業ルートとして最優先で当たる価値がある</t>
+        </is>
+      </c>
+      <c r="I45" s="31" t="inlineStr">
+        <is>
+          <t>終期確認と併せて道の市町村支援メニューを確認</t>
+        </is>
+      </c>
+      <c r="J45" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K41" s="31" t="inlineStr">
-        <is>
-          <t>外部DB（06シート 行181）</t>
+      <c r="K45" s="31" t="inlineStr">
+        <is>
+          <t>北海道 環境生活部環境政策課</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>義務（県）</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>第3次秋田県環境基本計画</t>
+        </is>
+      </c>
+      <c r="F46" s="30" t="inlineStr">
+        <is>
+          <t>令和3年度〜（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G46" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H46" s="30" t="inlineStr">
+        <is>
+          <t>令和3年3月31日策定。10年計画なら令和12年度満了だが未確認</t>
+        </is>
+      </c>
+      <c r="I46" s="30" t="inlineStr">
+        <is>
+          <t>終期を確認</t>
+        </is>
+      </c>
+      <c r="J46" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" s="30" t="inlineStr">
+        <is>
+          <t>秋田県 環境基本計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>義務（県）</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>福島県環境基本計画（第5次）</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="inlineStr">
+        <is>
+          <t>令和4年度〜（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G47" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H47" s="31" t="inlineStr">
+        <is>
+          <t>第4次が令和3年度で終了し、令和3年11月の環境審議会答申を経て第5次を策定。終期は未確認</t>
+        </is>
+      </c>
+      <c r="I47" s="31" t="inlineStr">
+        <is>
+          <t>終期を確認</t>
+        </is>
+      </c>
+      <c r="J47" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="31" t="inlineStr">
+        <is>
+          <t>福島県 環境基本計画（第5次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t>函館市</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>義務（中核市）</t>
+        </is>
+      </c>
+      <c r="E48" s="30" t="inlineStr">
+        <is>
+          <t>函館市環境基本計画［第3次計画］</t>
+        </is>
+      </c>
+      <c r="F48" s="30" t="inlineStr">
+        <is>
+          <t>令和2年度〜（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H48" s="30" t="inlineStr">
+        <is>
+          <t>令和2年3月策定。複数回検索したが終期はHTML上で確認できず。8年計画なら令和9年度満了で該当するため、確認優先度が最も高い</t>
+        </is>
+      </c>
+      <c r="I48" s="30" t="inlineStr">
+        <is>
+          <t>計画PDFで終期を最優先確認</t>
+        </is>
+      </c>
+      <c r="J48" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="30" t="inlineStr">
+        <is>
+          <t>函館市／EPO北海道</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="31" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>青森市</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="inlineStr">
+        <is>
+          <t>義務（中核市）</t>
+        </is>
+      </c>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>環境基本計画は確認できず（地球温暖化対策実行計画はあり）</t>
+        </is>
+      </c>
+      <c r="F49" s="31" t="inlineStr">
+        <is>
+          <t>（計画の有無から要確認）</t>
+        </is>
+      </c>
+      <c r="G49" s="31" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="H49" s="31" t="inlineStr">
+        <is>
+          <t>検索では環境基本計画を確認できず。区域施策編（令和7年3月改定）・事務事業編（第4期）はある。中核市のため区域施策編は策定義務</t>
+        </is>
+      </c>
+      <c r="I49" s="31" t="inlineStr">
+        <is>
+          <t>環境基本計画の有無そのものを確認。未策定なら新規策定提案の対象</t>
+        </is>
+      </c>
+      <c r="J49" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K49" s="31" t="inlineStr">
+        <is>
+          <t>青森市サイト</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B50" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t>帯広市</t>
+        </is>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>第三期帯広市環境基本計画</t>
+        </is>
+      </c>
+      <c r="F50" s="30" t="inlineStr">
+        <is>
+          <t>令和2年度〜（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G50" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H50" s="30" t="inlineStr">
+        <is>
+          <t>令和2年3月策定。第二期は平成22年度〜平成31年度</t>
+        </is>
+      </c>
+      <c r="I50" s="30" t="inlineStr">
+        <is>
+          <t>計画PDFで終期を確認</t>
+        </is>
+      </c>
+      <c r="J50" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K50" s="30" t="inlineStr">
+        <is>
+          <t>帯広市 第三期環境基本計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="31" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>北広島市</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>第3次北広島市環境基本計画</t>
+        </is>
+      </c>
+      <c r="F51" s="31" t="inlineStr">
+        <is>
+          <t>令和3年度〜（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G51" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H51" s="31" t="inlineStr">
+        <is>
+          <t>第2次が令和2年度で10年の期間を終了。令和5年2月のゼロカーボンシティ宣言を受け令和5年4月に地球環境分野を一部改定</t>
+        </is>
+      </c>
+      <c r="I51" s="31" t="inlineStr">
+        <is>
+          <t>計画PDFで終期を確認</t>
+        </is>
+      </c>
+      <c r="J51" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K51" s="31" t="inlineStr">
+        <is>
+          <t>北広島市 第3次環境基本計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t>北見市</t>
+        </is>
+      </c>
+      <c r="D52" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E52" s="30" t="inlineStr">
+        <is>
+          <t>第2次北見市環境基本計画（改定版）</t>
+        </is>
+      </c>
+      <c r="F52" s="30" t="inlineStr">
+        <is>
+          <t>（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H52" s="30" t="inlineStr">
+        <is>
+          <t>改定版の掲載を確認。計画期間はHTML上で読めず</t>
+        </is>
+      </c>
+      <c r="I52" s="30" t="inlineStr">
+        <is>
+          <t>計画PDFで計画期間を確認</t>
+        </is>
+      </c>
+      <c r="J52" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K52" s="30" t="inlineStr">
+        <is>
+          <t>北見市 第2次環境基本計画（改定版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="31" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="C53" s="31" t="inlineStr">
+        <is>
+          <t>大崎市</t>
+        </is>
+      </c>
+      <c r="D53" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E53" s="31" t="inlineStr">
+        <is>
+          <t>第2次大崎市環境基本計画</t>
+        </is>
+      </c>
+      <c r="F53" s="31" t="inlineStr">
+        <is>
+          <t>令和2年度〜（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G53" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H53" s="31" t="inlineStr">
+        <is>
+          <t>令和2年3月策定・10年後を見据えた計画。アクションプランも別途あり</t>
+        </is>
+      </c>
+      <c r="I53" s="31" t="inlineStr">
+        <is>
+          <t>計画PDFで終期を確認</t>
+        </is>
+      </c>
+      <c r="J53" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K53" s="31" t="inlineStr">
+        <is>
+          <t>大崎市 第2次環境基本計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B54" s="30" t="inlineStr">
+        <is>
+          <t>山形県</t>
+        </is>
+      </c>
+      <c r="C54" s="30" t="inlineStr">
+        <is>
+          <t>鶴岡市</t>
+        </is>
+      </c>
+      <c r="D54" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E54" s="30" t="inlineStr">
+        <is>
+          <t>第2次鶴岡市環境基本計画</t>
+        </is>
+      </c>
+      <c r="F54" s="30" t="inlineStr">
+        <is>
+          <t>（終期未確認）</t>
+        </is>
+      </c>
+      <c r="G54" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="H54" s="30" t="inlineStr">
+        <is>
+          <t>第2次の掲載を確認。計画期間はHTML上で読めず</t>
+        </is>
+      </c>
+      <c r="I54" s="30" t="inlineStr">
+        <is>
+          <t>計画PDFで計画期間を確認</t>
+        </is>
+      </c>
+      <c r="J54" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K54" s="30" t="inlineStr">
+        <is>
+          <t>鶴岡市 第2次環境基本計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="31" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>十和田市</t>
+        </is>
+      </c>
+      <c r="D55" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>環境基本計画は確認できず（環境保全率先行動計画・温対実行計画はあり）</t>
+        </is>
+      </c>
+      <c r="F55" s="31" t="inlineStr">
+        <is>
+          <t>（計画の有無から要確認）</t>
+        </is>
+      </c>
+      <c r="G55" s="31" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="H55" s="31" t="inlineStr">
+        <is>
+          <t>環境保全率先行動計画『とわだエコ・オフィスプラン』第5次が令和4年4月から令和8年度で満了。これを入口に環境基本計画の有無を確認する</t>
+        </is>
+      </c>
+      <c r="I55" s="31" t="inlineStr">
+        <is>
+          <t>率先行動計画の改定を入口に接触</t>
+        </is>
+      </c>
+      <c r="J55" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K55" s="31" t="inlineStr">
+        <is>
+          <t>十和田市サイト</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>？要確認</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C56" s="30" t="inlineStr">
+        <is>
+          <t>小樽市</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>（環境基本計画の期間を確認できず）</t>
+        </is>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
+        <is>
+          <t>（未確認）</t>
+        </is>
+      </c>
+      <c r="G56" s="30" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="H56" s="30" t="inlineStr">
+        <is>
+          <t>『小樽市の環境』（年次報告）と緑の基本計画は確認できるが、環境基本計画の期間は確認できず</t>
+        </is>
+      </c>
+      <c r="I56" s="30" t="inlineStr">
+        <is>
+          <t>計画一覧・生活環境部ページで継続確認</t>
+        </is>
+      </c>
+      <c r="J56" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K56" s="30" t="inlineStr">
+        <is>
+          <t>小樽市サイト</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K41"/>
-  <mergeCells count="10">
-    <mergeCell ref="A34:K34"/>
+  <autoFilter ref="A2:K56"/>
+  <mergeCells count="11">
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A20:K20"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A44:K44"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3207,22 +4052,22 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>一部確認（策定年のみ）</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>北海道 環境生活部環境政策課（令和3年3月策定）。終期を要確認</t>
+          <t>北海道 環境生活部環境政策課。令和3年3月策定。複数回検索したが終期はHTML上で確認できず、計画本文の確認が必要</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>優先（義務団体・県ルート）</t>
+          <t>優先（義務団体・道ルート）</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>終期の確認と併せて、道の市町村支援・共同策定の枠組みを確認する。営業ルートの選択に直結する</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
@@ -3262,7 +4107,7 @@
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>青森県環境総合プラン</t>
+          <t>第6次青森県環境計画（青森県環境総合プラン）</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -3270,30 +4115,34 @@
           <t>令和6年度(2024)</t>
         </is>
       </c>
-      <c r="I4" s="24" t="inlineStr"/>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>令和10年度(2028)</t>
+        </is>
+      </c>
       <c r="J4" s="24" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>非該当</t>
         </is>
       </c>
       <c r="K4" s="24" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L4" s="24" t="inlineStr">
         <is>
-          <t>青森県 環境政策課（令和6年3月）。終期を要確認</t>
+          <t>青森県 第6次青森県環境計画（令和6年3月）。計画期間は令和6〜10年度の5年間</t>
         </is>
       </c>
       <c r="M4" s="24" t="inlineStr">
         <is>
-          <t>優先（義務団体・県ルート）</t>
+          <t>中（R10満了・R9夏に予算要求期）</t>
         </is>
       </c>
       <c r="N4" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>令和10年度満了のため改定業務は令和10年度。県への接触は令和9年度の夏〜秋。並行して県の市町村支援メニューを確認する</t>
         </is>
       </c>
       <c r="O4" s="24" t="inlineStr">
@@ -3406,32 +4255,44 @@
           <t>義務</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr"/>
-      <c r="H6" s="24" t="inlineStr"/>
-      <c r="I6" s="24" t="inlineStr"/>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>宮城県環境基本計画（第4期）</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>令和12年度(2030)</t>
+        </is>
+      </c>
       <c r="J6" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>非該当</t>
         </is>
       </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>県の環境政策担当課ページ</t>
+          <t>宮城県公式サイト 環境基本計画（第4期）。計画期間は令和3年度〜令和12年度</t>
         </is>
       </c>
       <c r="M6" s="24" t="inlineStr">
         <is>
-          <t>優先（義務団体・県ルート）</t>
+          <t>中（県ルート）</t>
         </is>
       </c>
       <c r="N6" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>令和12年度満了。期間中は県の市町村支援・共同策定の枠組みの有無を確認する</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -3469,22 +4330,30 @@
           <t>義務</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>第3次秋田県環境基本計画</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>一部確認（策定年のみ）</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>県の環境政策担当課ページ</t>
+          <t>秋田県 環境基本計画。第3次を令和3年3月31日に策定。終期は未確認。なお第4次秋田県循環型社会形成推進基本計画は令和3年度〜令和7年度</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -3494,7 +4363,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>計画本文で終期を確認する。10年計画なら令和12年度満了</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -3534,34 +4403,42 @@
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>第3次山形県環境計画</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="inlineStr"/>
-      <c r="I8" s="24" t="inlineStr"/>
+          <t>第4次山形県環境計画</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>令和12年度(2030)</t>
+        </is>
+      </c>
       <c r="J8" s="24" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>非該当</t>
         </is>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>山形県 環境企画課。期間を要確認</t>
+          <t>山形県公式サイト 第4次山形県環境計画（令和3年3月策定・10年間）。従前リストの『第3次』は平成23年度〜令和2年度で終了済のため計画名を訂正</t>
         </is>
       </c>
       <c r="M8" s="24" t="inlineStr">
         <is>
-          <t>優先（義務団体・県ルート）</t>
+          <t>中（県ルート）</t>
         </is>
       </c>
       <c r="N8" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>令和12年度満了。期間中は県の市町村支援・共同策定の枠組みの有無を確認する</t>
         </is>
       </c>
       <c r="O8" s="24" t="inlineStr">
@@ -3599,22 +4476,30 @@
           <t>義務</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>福島県環境基本計画（第5次）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>令和4年度(2022)</t>
+        </is>
+      </c>
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>一部確認（次数・前計画の終了年のみ）</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>県の環境政策担当課ページ</t>
+          <t>福島県 環境基本計画（第5次）。第4次が令和3年度で終了し、令和3年11月の環境審議会答申を経て第5次を策定。終期は未確認</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -3624,7 +4509,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>計画本文で計画期間を確認する</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -3733,32 +4618,44 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>えべつアジェンダ21―江別市環境管理計画―</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>平成7年度(1995)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>計画期間30年（終期到来・後継未確認）</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>◇満了期・後継要確認</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済（30年計画・後期推進計画は令和5年度終了）</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>江別市 環境管理計画。平成7年度に計画期間30年で策定。後期推進計画は平成26年度から令和5年度で終了済。後継計画の状況は未確認</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>優先（満了期・後継未確認）</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>30年計画の終期が到来し、後期推進計画も令和5年度で終了している。後継計画の有無と策定予定を早急に確認する</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr"/>
@@ -3792,32 +4689,44 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr"/>
-      <c r="H12" s="24" t="inlineStr"/>
-      <c r="I12" s="24" t="inlineStr"/>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>第3次千歳市環境基本計画</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>令和12年度(2030)</t>
+        </is>
+      </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>非該当</t>
         </is>
       </c>
       <c r="K12" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>千歳市 第3次環境基本計画（令和3年度〜令和12年度）</t>
         </is>
       </c>
       <c r="M12" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低（期間先）</t>
         </is>
       </c>
       <c r="N12" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>令和12年度満了。次期改定は令和11年度頃から予算化を確認する</t>
         </is>
       </c>
       <c r="O12" s="24" t="inlineStr"/>
@@ -3915,7 +4824,11 @@
           <t>第3次北広島市環境基本計画</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr"/>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
       <c r="I14" s="24" t="inlineStr"/>
       <c r="J14" s="24" t="inlineStr">
         <is>
@@ -3924,22 +4837,22 @@
       </c>
       <c r="K14" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>一部確認（策定年・一部改定確認）</t>
         </is>
       </c>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>北広島市サイトに第3次計画の掲載あり。期間を要確認</t>
+          <t>北広島市 第3次環境基本計画。第2次が令和2年度で10年の期間を終了。令和5年2月のゼロカーボンシティ宣言を受け、令和5年4月に地球環境分野を一部改定</t>
         </is>
       </c>
       <c r="M14" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中（終期要確認・期間中改定の実例）</t>
         </is>
       </c>
       <c r="N14" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>計画PDFで終期を確認する。地球環境分野の一部改定実績があるため、国の2035年度目標を踏まえた再度の部分改定の余地もある</t>
         </is>
       </c>
       <c r="O14" s="24" t="inlineStr"/>
@@ -3975,34 +4888,42 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>石狩市環境基本計画</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
+          <t>石狩市環境基本計画（第3次）</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>令和5年度(2023)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>令和24年度(2042)頃（20年計画）</t>
+        </is>
+      </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>非該当</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済（20年計画）</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>石狩市サイトに掲載あり。期間を要確認</t>
+          <t>石狩市 環境基本計画。令和5年3月策定・計画期間20年。第2次は令和2年度で終了</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低（20年計画）</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>20年計画のため改定需要は当面ない。中間見直しの規定の有無だけ確認する</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr"/>
@@ -4172,22 +5093,22 @@
       </c>
       <c r="K18" s="24" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>一部確認（策定年のみ）</t>
         </is>
       </c>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>函館市／追加周期表でも計画期間は未確認。令和2年3月策定・第3次計画案への導線は確認済だが、終期は公式PDFで要確認</t>
+          <t>函館市／EPO北海道。令和2年3月策定。複数回検索したが終期はHTML上で確認できず、計画PDFの確認が必要。総合計画は2017〜2026年</t>
         </is>
       </c>
       <c r="M18" s="24" t="inlineStr">
         <is>
-          <t>優先（義務団体・終期要確認）</t>
+          <t>最優先（義務団体・終期要確認）</t>
         </is>
       </c>
       <c r="N18" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で終期を最優先確認。8年計画ならR9満了、10年ならR11満了として扱う</t>
+          <t>計画PDFの表紙・第1章で終期を最優先確認する。8年計画なら令和9年度満了で該当、10年なら令和11年度満了</t>
         </is>
       </c>
       <c r="O18" s="24" t="inlineStr"/>
@@ -5229,27 +6150,27 @@
       <c r="I36" s="24" t="inlineStr"/>
       <c r="J36" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="K36" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>公式検索確認</t>
         </is>
       </c>
       <c r="L36" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>小樽市サイト・検索では環境基本計画の計画期間を確認できず。『小樽市の環境』（年次報告）と緑の基本計画は確認できる</t>
         </is>
       </c>
       <c r="M36" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中（未確認継続）</t>
         </is>
       </c>
       <c r="N36" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>公式の計画一覧・生活環境部のページで環境基本計画の有無とPDFを継続確認する</t>
         </is>
       </c>
       <c r="O36" s="24" t="inlineStr"/>
@@ -10251,32 +11172,36 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G121" s="4" t="inlineStr"/>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>第2次北見市環境基本計画（改定版）</t>
+        </is>
+      </c>
       <c r="H121" s="4" t="inlineStr"/>
       <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>一部確認（計画掲載確認）</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>北見市 第2次環境基本計画（改定版）の掲載を確認。計画期間はHTML上で読めず、PDF確認が必要</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中（終期要確認）</t>
         </is>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>計画PDFで計画期間を確認する</t>
         </is>
       </c>
       <c r="O121" s="4" t="inlineStr"/>
@@ -12517,10 +13442,14 @@
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>帯広市環境基本計画（第三期）</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr"/>
+          <t>第三期帯広市環境基本計画</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>令和2年度(2020)</t>
+        </is>
+      </c>
       <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -12529,22 +13458,22 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>一部確認（策定年のみ）</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>第二期が平成22年度〜平成31年度。第三期の期間を要確認</t>
+          <t>帯広市 第三期環境基本計画（令和2年3月策定）。第二期は平成22年度〜平成31年度。終期はPDF確認が必要</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中（終期要確認）</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>計画PDFで終期を確認する。10年計画なら令和11年度満了</t>
         </is>
       </c>
       <c r="O157" s="4" t="inlineStr"/>
@@ -13796,32 +14725,44 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G176" s="24" t="inlineStr"/>
-      <c r="H176" s="24" t="inlineStr"/>
-      <c r="I176" s="24" t="inlineStr"/>
+      <c r="G176" s="24" t="inlineStr">
+        <is>
+          <t>第2次釧路市環境基本計画【改定版】</t>
+        </is>
+      </c>
+      <c r="H176" s="24" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
+      <c r="I176" s="24" t="inlineStr">
+        <is>
+          <t>令和12年度(2030)</t>
+        </is>
+      </c>
       <c r="J176" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>非該当（令和6年3月に一部改定）</t>
         </is>
       </c>
       <c r="K176" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L176" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>釧路市 第2次環境基本計画【改定版】。計画期間は令和3年度〜令和12年度。国・北海道の温暖化計画改定を受け、低炭素社会の形成の目標を令和6年3月に改定</t>
         </is>
       </c>
       <c r="M176" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中（期間中改定の実例）</t>
         </is>
       </c>
       <c r="N176" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>計画期間中だが低炭素分野を一部改定した実績がある。国の2035年度目標を踏まえた再度の部分改定の余地を確認する</t>
         </is>
       </c>
       <c r="O176" s="24" t="inlineStr"/>
@@ -14619,32 +15560,36 @@
           <t>義務</t>
         </is>
       </c>
-      <c r="G189" s="4" t="inlineStr"/>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>環境基本計画は確認できず（関連：地球温暖化対策実行計画）</t>
+        </is>
+      </c>
       <c r="H189" s="4" t="inlineStr"/>
       <c r="I189" s="4" t="inlineStr"/>
       <c r="J189" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>要確認（環境基本計画の有無から）</t>
         </is>
       </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>公式検索確認</t>
         </is>
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>青森市／追加周期表でも環境基本計画の直接掲載・期間は未確認。中核市のため要確認を継続</t>
+          <t>青森市サイト・検索では環境基本計画を確認できず。地球温暖化対策実行計画（区域施策編 令和7年3月改定／事務事業編 第4期）は確認できる。中核市のため区域施策編は策定義務</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>優先（義務団体・終期要確認）</t>
+          <t>最優先（義務団体・計画の有無から確認）</t>
         </is>
       </c>
       <c r="N189" s="4" t="inlineStr">
         <is>
-          <t>公式サイト内検索・計画一覧・環境白書から計画名と期間を確認する</t>
+          <t>環境基本計画の有無そのものを確認する。未策定なら新規策定提案の対象。策定済みなら計画名が異なる可能性があるため計画一覧から探す</t>
         </is>
       </c>
       <c r="O189" s="4" t="inlineStr"/>
@@ -15752,32 +16697,36 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G208" s="24" t="inlineStr"/>
+      <c r="G208" s="24" t="inlineStr">
+        <is>
+          <t>環境基本計画は確認できず（関連：環境保全率先行動計画・地球温暖化対策実行計画）</t>
+        </is>
+      </c>
       <c r="H208" s="24" t="inlineStr"/>
       <c r="I208" s="24" t="inlineStr"/>
       <c r="J208" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>要確認（環境基本計画の有無から）</t>
         </is>
       </c>
       <c r="K208" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>公式検索確認</t>
         </is>
       </c>
       <c r="L208" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>十和田市サイト・検索では環境基本計画を確認できず。環境保全率先行動計画『とわだエコ・オフィスプラン』第5次が令和4年4月から令和8年度、地球温暖化対策実行計画（区域施策編）は確認できる</t>
         </is>
       </c>
       <c r="M208" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中（関連計画がR8満了）</t>
         </is>
       </c>
       <c r="N208" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>環境保全率先行動計画が令和8年度で満了するため、その改定を入口に環境基本計画の有無を確認する</t>
         </is>
       </c>
       <c r="O208" s="24" t="inlineStr"/>
@@ -17664,32 +18613,44 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G240" s="24" t="inlineStr"/>
-      <c r="H240" s="24" t="inlineStr"/>
-      <c r="I240" s="24" t="inlineStr"/>
+      <c r="G240" s="24" t="inlineStr">
+        <is>
+          <t>一関市環境基本計画</t>
+        </is>
+      </c>
+      <c r="H240" s="24" t="inlineStr">
+        <is>
+          <t>平成29年度(2017)</t>
+        </is>
+      </c>
+      <c r="I240" s="24" t="inlineStr">
+        <is>
+          <t>令和8年度(2026)</t>
+        </is>
+      </c>
       <c r="J240" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>◇今年度が改定年度（R8満了）</t>
         </is>
       </c>
       <c r="K240" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L240" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>一関市 生活環境課 環境基本計画。計画期間は平成29年度から令和8年度。なお市の地球温暖化対策地域推進計画は令和5年度〜令和12年度</t>
         </is>
       </c>
       <c r="M240" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>最優先（今年度満了）</t>
         </is>
       </c>
       <c r="N240" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>令和8年度末で満了＝次期計画は令和9年度開始。改定業務は今年度に実施されるため、既発注か自前策定かを直ちに確認する。発注済みなら範囲外の支援に絞る</t>
         </is>
       </c>
       <c r="O240" s="24" t="inlineStr"/>
@@ -20272,32 +21233,44 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G284" s="24" t="inlineStr"/>
-      <c r="H284" s="24" t="inlineStr"/>
-      <c r="I284" s="24" t="inlineStr"/>
+      <c r="G284" s="24" t="inlineStr">
+        <is>
+          <t>石巻市環境基本計画（第2次）</t>
+        </is>
+      </c>
+      <c r="H284" s="24" t="inlineStr">
+        <is>
+          <t>令和8年度(2026)</t>
+        </is>
+      </c>
+      <c r="I284" s="24" t="inlineStr">
+        <is>
+          <t>令和17年度(2035)</t>
+        </is>
+      </c>
       <c r="J284" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>非該当（令和8年3月策定）</t>
         </is>
       </c>
       <c r="K284" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L284" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>石巻市 環境基本計画（案）令和8年。令和8年度から10年間、目標年度は令和17年度</t>
         </is>
       </c>
       <c r="M284" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低（策定直後）</t>
         </is>
       </c>
       <c r="N284" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>策定直後のため新規受託は難しい。進捗管理・アンケート二次分析など周辺支援の余地を確認する</t>
         </is>
       </c>
       <c r="O284" s="24" t="inlineStr"/>
@@ -20626,32 +21599,40 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G290" s="24" t="inlineStr"/>
-      <c r="H290" s="24" t="inlineStr"/>
+      <c r="G290" s="24" t="inlineStr">
+        <is>
+          <t>第2次大崎市環境基本計画</t>
+        </is>
+      </c>
+      <c r="H290" s="24" t="inlineStr">
+        <is>
+          <t>令和2年度(2020)</t>
+        </is>
+      </c>
       <c r="I290" s="24" t="inlineStr"/>
       <c r="J290" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="K290" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>一部確認（策定年のみ）</t>
         </is>
       </c>
       <c r="L290" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>大崎市 第2次環境基本計画（令和2年3月策定・10年後を見据えた計画）。アクションプランも別途あり。終期はPDF確認が必要</t>
         </is>
       </c>
       <c r="M290" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中（終期要確認）</t>
         </is>
       </c>
       <c r="N290" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>計画PDFで終期を確認する。10年計画なら令和11年度満了</t>
         </is>
       </c>
       <c r="O290" s="24" t="inlineStr"/>
@@ -23836,32 +24817,36 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G344" s="24" t="inlineStr"/>
+      <c r="G344" s="24" t="inlineStr">
+        <is>
+          <t>第2次鶴岡市環境基本計画</t>
+        </is>
+      </c>
       <c r="H344" s="24" t="inlineStr"/>
       <c r="I344" s="24" t="inlineStr"/>
       <c r="J344" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>要確認</t>
         </is>
       </c>
       <c r="K344" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>一部確認（計画掲載確認）</t>
         </is>
       </c>
       <c r="L344" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>鶴岡市 第2次環境基本計画の掲載を確認。計画期間はHTML上で読めず、PDF確認が必要</t>
         </is>
       </c>
       <c r="M344" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>中（終期要確認）</t>
         </is>
       </c>
       <c r="N344" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>計画PDFで計画期間を確認する</t>
         </is>
       </c>
       <c r="O344" s="24" t="inlineStr"/>
@@ -24605,7 +25590,7 @@
       </c>
       <c r="G357" s="4" t="inlineStr">
         <is>
-          <t>福島市環境基本計画</t>
+          <t>第3次福島市環境基本計画</t>
         </is>
       </c>
       <c r="H357" s="4" t="inlineStr">
@@ -24613,30 +25598,34 @@
           <t>令和3年度(2021)</t>
         </is>
       </c>
-      <c r="I357" s="4" t="inlineStr"/>
+      <c r="I357" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度(2025)</t>
+        </is>
+      </c>
       <c r="J357" s="4" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>満了済（第4次の期間を要確認）</t>
         </is>
       </c>
       <c r="K357" s="4" t="inlineStr">
         <is>
-          <t>一部確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L357" s="4" t="inlineStr">
         <is>
-          <t>福島市／追加周期表でも計画期間は未確認。新環境基本計画・脱炭素社会実現実行計画の策定動向は確認済</t>
+          <t>福島市公式サイト 環境基本計画（令和3年2月策定）。計画期間は令和3年度〜令和7年度の5年間。5年周期のため次の満了も早く来る</t>
         </is>
       </c>
       <c r="M357" s="4" t="inlineStr">
         <is>
-          <t>優先（義務団体・策定動向確認）</t>
+          <t>優先（義務団体・満了済）</t>
         </is>
       </c>
       <c r="N357" s="4" t="inlineStr">
         <is>
-          <t>新計画本文・予算・審議会資料を確認。期間満了ではなく新計画策定支援・脱炭素実行計画連携の可能性を確認する</t>
+          <t>令和7年度末で満了済。第4次の策定状況を早急に確認する。策定済みなら次期（令和12年度頃）に向けた関係構築、未策定なら補正・当初での策定提案</t>
         </is>
       </c>
       <c r="O357" s="4" t="inlineStr"/>
@@ -26334,32 +27323,44 @@
           <t>努力義務</t>
         </is>
       </c>
-      <c r="G386" s="24" t="inlineStr"/>
-      <c r="H386" s="24" t="inlineStr"/>
-      <c r="I386" s="24" t="inlineStr"/>
+      <c r="G386" s="24" t="inlineStr">
+        <is>
+          <t>会津若松市第3期環境基本計画</t>
+        </is>
+      </c>
+      <c r="H386" s="24" t="inlineStr">
+        <is>
+          <t>令和6年度(2024)</t>
+        </is>
+      </c>
+      <c r="I386" s="24" t="inlineStr">
+        <is>
+          <t>令和12年度(2030)</t>
+        </is>
+      </c>
       <c r="J386" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>非該当</t>
         </is>
       </c>
       <c r="K386" s="24" t="inlineStr">
         <is>
-          <t>未確認</t>
+          <t>確認済</t>
         </is>
       </c>
       <c r="L386" s="24" t="inlineStr">
         <is>
-          <t>団体サイトの環境基本計画ページ</t>
+          <t>会津若松市 第3期環境基本計画（令和6年3月策定・7年間）</t>
         </is>
       </c>
       <c r="M386" s="24" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低（期間先）</t>
         </is>
       </c>
       <c r="N386" s="24" t="inlineStr">
         <is>
-          <t>計画PDFの表紙・第1章で計画期間を確認し、終期欄を埋める</t>
+          <t>令和12年度満了。次期改定は令和11年度頃から予算化を確認する</t>
         </is>
       </c>
       <c r="O386" s="24" t="inlineStr"/>
@@ -28087,6 +29088,7 @@
       </c>
       <c r="O415" s="4" t="inlineStr"/>
     </row>
+    <row r="416"/>
     <row r="417">
       <c r="A417" s="6" t="inlineStr">
         <is>
@@ -29164,7 +30166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.5" customWidth="1" min="1" max="1"/>
@@ -29504,6 +30506,33 @@
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>encodinginvestigation.md ／ naming.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-25 改定時期調査 第2回</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>義務団体9件・主要市14件の未確認先</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>計画期間を調査。終期を特定できた11件を確認済へ、計画名・策定年のみの9件を一部確認へ、環境基本計画を確認できなかった3件を計画未確認へ更新</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>一関市はR8年度末満了で今年度が改定年度＝直ちに接触。福島市（中核市）はR3〜R7で満了済、江別市は30年計画の終期到来で後継未確認。いずれもR9満了先より先に動く</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>08_改定時期調査_20260825b</t>
         </is>
       </c>
     </row>
@@ -31696,9 +32725,6 @@
           <t>⑦ 提出仕様（ファイル名・文字コード）｜ 文字コード調査報告の結論を本ブックへ適用したもの</t>
         </is>
       </c>
-      <c r="B1" s="26" t="n"/>
-      <c r="C1" s="26" t="n"/>
-      <c r="D1" s="26" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
@@ -31728,9 +32754,9 @@
           <t>■ 結論（文字コード調査報告より）</t>
         </is>
       </c>
-      <c r="B3" s="29" t="n"/>
-      <c r="C3" s="29" t="n"/>
-      <c r="D3" s="29" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="36" t="n"/>
+      <c r="D3" s="37" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
@@ -31804,9 +32830,9 @@
           <t>■ 本ブックのCP932変換可否（2026-08-25 検査）</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="29" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="37" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="30" t="inlineStr">
@@ -31902,9 +32928,9 @@
           <t>■ 提出用の出力（output/csv/）</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n"/>
-      <c r="C12" s="29" t="n"/>
-      <c r="D12" s="29" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="37" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
@@ -32066,9 +33092,9 @@
           <t>■ ファイル名</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n"/>
-      <c r="C20" s="29" t="n"/>
-      <c r="D20" s="29" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
@@ -32186,9 +33212,9 @@
           <t>■ 運用</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="29" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="37" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
@@ -32284,9 +33310,9 @@
           <t>■ 未確認事項</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="29" t="n"/>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="37" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
@@ -32338,9 +33364,6 @@
           <t>提出前に必ず確認すること: 提出先システム名／アップロード時の実際のエラーメッセージ／要求されるファイル形式・文字コード・ファイル名の制約。この3点が揃うまで、原因を文字コードと断定しないこと。</t>
         </is>
       </c>
-      <c r="B35" s="33" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:D33"/>
@@ -32356,4 +33379,1510 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>⑧ 改定時期調査（2026-08-25 第2回）｜ 義務団体・主要市の未確認先を優先に確認</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="26" t="n"/>
+      <c r="I1" s="26" t="n"/>
+      <c r="J1" s="26" t="n"/>
+      <c r="K1" s="26" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>自治体</t>
+        </is>
+      </c>
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>義務区分</t>
+        </is>
+      </c>
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>調査結果</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>計画名</t>
+        </is>
+      </c>
+      <c r="G2" s="27" t="inlineStr">
+        <is>
+          <t>計画期間</t>
+        </is>
+      </c>
+      <c r="H2" s="27" t="inlineStr">
+        <is>
+          <t>R9満了判定</t>
+        </is>
+      </c>
+      <c r="I2" s="27" t="inlineStr">
+        <is>
+          <t>確認状況</t>
+        </is>
+      </c>
+      <c r="J2" s="27" t="inlineStr">
+        <is>
+          <t>根拠・確認メモ</t>
+        </is>
+      </c>
+      <c r="K2" s="27" t="inlineStr">
+        <is>
+          <t>次確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>■ 終期を特定できた先（確認済）</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="n"/>
+      <c r="C3" s="29" t="n"/>
+      <c r="D3" s="29" t="n"/>
+      <c r="E3" s="29" t="n"/>
+      <c r="F3" s="29" t="n"/>
+      <c r="G3" s="29" t="n"/>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="29" t="n"/>
+      <c r="J3" s="29" t="n"/>
+      <c r="K3" s="29" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>第6次青森県環境計画（青森県環境総合プラン）</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>令和6年度(2024)〜令和10年度(2028)</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>青森県 第6次青森県環境計画（令和6年3月）。計画期間は令和6〜10年度の5年間</t>
+        </is>
+      </c>
+      <c r="K4" s="30" t="inlineStr">
+        <is>
+          <t>令和10年度満了のため改定業務は令和10年度。県への接触は令和9年度の夏〜秋。並行して県の市町村支援メニューを確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>宮城県環境基本計画（第4期）</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)〜令和12年度(2030)</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>宮城県公式サイト 環境基本計画（第4期）。計画期間は令和3年度〜令和12年度</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr">
+        <is>
+          <t>令和12年度満了。期間中は県の市町村支援・共同策定の枠組みの有無を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>山形県</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>山形県</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>第4次山形県環境計画</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)〜令和12年度(2030)</t>
+        </is>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="I6" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>山形県公式サイト 第4次山形県環境計画（令和3年3月策定・10年間）。従前リストの『第3次』は平成23年度〜令和2年度で終了済のため計画名を訂正</t>
+        </is>
+      </c>
+      <c r="K6" s="30" t="inlineStr">
+        <is>
+          <t>令和12年度満了。期間中は県の市町村支援・共同策定の枠組みの有無を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>福島市</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>第3次福島市環境基本計画</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)〜令和7年度(2025)</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>満了済（第4次の期間を要確認）</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>福島市公式サイト 環境基本計画（令和3年2月策定）。計画期間は令和3年度〜令和7年度の5年間。5年周期のため次の満了も早く来る</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr">
+        <is>
+          <t>令和7年度末で満了済。第4次の策定状況を早急に確認する。策定済みなら次期（令和12年度頃）に向けた関係構築、未策定なら補正・当初での策定提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>一関市</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>一関市環境基本計画</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>平成29年度(2017)〜令和8年度(2026)</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>◇今年度が改定年度（R8満了）</t>
+        </is>
+      </c>
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>一関市 生活環境課 環境基本計画。計画期間は平成29年度から令和8年度。なお市の地球温暖化対策地域推進計画は令和5年度〜令和12年度</t>
+        </is>
+      </c>
+      <c r="K8" s="30" t="inlineStr">
+        <is>
+          <t>令和8年度末で満了＝次期計画は令和9年度開始。改定業務は今年度に実施されるため、既発注か自前策定かを直ちに確認する。発注済みなら範囲外の支援に絞る</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>会津若松市</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>会津若松市第3期環境基本計画</t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>令和6年度(2024)〜令和12年度(2030)</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="I9" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>会津若松市 第3期環境基本計画（令和6年3月策定・7年間）</t>
+        </is>
+      </c>
+      <c r="K9" s="31" t="inlineStr">
+        <is>
+          <t>令和12年度満了。次期改定は令和11年度頃から予算化を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>釧路市</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>第2次釧路市環境基本計画【改定版】</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)〜令和12年度(2030)</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>非該当（令和6年3月に一部改定）</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>釧路市 第2次環境基本計画【改定版】。計画期間は令和3年度〜令和12年度。国・北海道の温暖化計画改定を受け、低炭素社会の形成の目標を令和6年3月に改定</t>
+        </is>
+      </c>
+      <c r="K10" s="30" t="inlineStr">
+        <is>
+          <t>計画期間中だが低炭素分野を一部改定した実績がある。国の2035年度目標を踏まえた再度の部分改定の余地を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>千歳市</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>第3次千歳市環境基本計画</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)〜令和12年度(2030)</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="I11" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>千歳市 第3次環境基本計画（令和3年度〜令和12年度）</t>
+        </is>
+      </c>
+      <c r="K11" s="31" t="inlineStr">
+        <is>
+          <t>令和12年度満了。次期改定は令和11年度頃から予算化を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>石狩市</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>石狩市環境基本計画（第3次）</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>令和5年度(2023)〜令和24年度(2042)頃（20年計画）</t>
+        </is>
+      </c>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>非該当</t>
+        </is>
+      </c>
+      <c r="I12" s="30" t="inlineStr">
+        <is>
+          <t>確認済（20年計画）</t>
+        </is>
+      </c>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>石狩市 環境基本計画。令和5年3月策定・計画期間20年。第2次は令和2年度で終了</t>
+        </is>
+      </c>
+      <c r="K12" s="30" t="inlineStr">
+        <is>
+          <t>20年計画のため改定需要は当面ない。中間見直しの規定の有無だけ確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>石巻市</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>石巻市環境基本計画（第2次）</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>令和8年度(2026)〜令和17年度(2035)</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>非該当（令和8年3月策定）</t>
+        </is>
+      </c>
+      <c r="I13" s="31" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>石巻市 環境基本計画（案）令和8年。令和8年度から10年間、目標年度は令和17年度</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>策定直後のため新規受託は難しい。進捗管理・アンケート二次分析など周辺支援の余地を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>終期確定</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>江別市</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>えべつアジェンダ21―江別市環境管理計画―</t>
+        </is>
+      </c>
+      <c r="G14" s="30" t="inlineStr">
+        <is>
+          <t>平成7年度(1995)〜計画期間30年（終期到来・後継未確認）</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>◇満了期・後継要確認</t>
+        </is>
+      </c>
+      <c r="I14" s="30" t="inlineStr">
+        <is>
+          <t>確認済（30年計画・後期推進計画は令和5年度終了）</t>
+        </is>
+      </c>
+      <c r="J14" s="30" t="inlineStr">
+        <is>
+          <t>江別市 環境管理計画。平成7年度に計画期間30年で策定。後期推進計画は平成26年度から令和5年度で終了済。後継計画の状況は未確認</t>
+        </is>
+      </c>
+      <c r="K14" s="30" t="inlineStr">
+        <is>
+          <t>30年計画の終期が到来し、後期推進計画も令和5年度で終了している。後継計画の有無と策定予定を早急に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>■ 計画名・策定年のみ判明（終期は未確認のまま。推測で埋めない）</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="29" t="n"/>
+      <c r="H15" s="29" t="n"/>
+      <c r="I15" s="29" t="n"/>
+      <c r="J15" s="29" t="n"/>
+      <c r="K15" s="29" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>北海道環境基本計画［第3次計画］</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I16" s="30" t="inlineStr">
+        <is>
+          <t>一部確認（策定年のみ）</t>
+        </is>
+      </c>
+      <c r="J16" s="30" t="inlineStr">
+        <is>
+          <t>北海道 環境生活部環境政策課。令和3年3月策定。複数回検索したが終期はHTML上で確認できず、計画本文の確認が必要</t>
+        </is>
+      </c>
+      <c r="K16" s="30" t="inlineStr">
+        <is>
+          <t>終期の確認と併せて、道の市町村支援・共同策定の枠組みを確認する。営業ルートの選択に直結する</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>第3次秋田県環境基本計画</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr">
+        <is>
+          <t>一部確認（策定年のみ）</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>秋田県 環境基本計画。第3次を令和3年3月31日に策定。終期は未確認。なお第4次秋田県循環型社会形成推進基本計画は令和3年度〜令和7年度</t>
+        </is>
+      </c>
+      <c r="K17" s="31" t="inlineStr">
+        <is>
+          <t>計画本文で終期を確認する。10年計画なら令和12年度満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>福島県環境基本計画（第5次）</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="inlineStr">
+        <is>
+          <t>令和4年度(2022)</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I18" s="30" t="inlineStr">
+        <is>
+          <t>一部確認（次数・前計画の終了年のみ）</t>
+        </is>
+      </c>
+      <c r="J18" s="30" t="inlineStr">
+        <is>
+          <t>福島県 環境基本計画（第5次）。第4次が令和3年度で終了し、令和3年11月の環境審議会答申を経て第5次を策定。終期は未確認</t>
+        </is>
+      </c>
+      <c r="K18" s="30" t="inlineStr">
+        <is>
+          <t>計画本文で計画期間を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>函館市</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>函館市環境基本計画［第3次計画］</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="inlineStr">
+        <is>
+          <t>令和2年度(2020)</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I19" s="31" t="inlineStr">
+        <is>
+          <t>一部確認（策定年のみ）</t>
+        </is>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>函館市／EPO北海道。令和2年3月策定。複数回検索したが終期はHTML上で確認できず、計画PDFの確認が必要。総合計画は2017〜2026年</t>
+        </is>
+      </c>
+      <c r="K19" s="31" t="inlineStr">
+        <is>
+          <t>計画PDFの表紙・第1章で終期を最優先確認する。8年計画なら令和9年度満了で該当、10年なら令和11年度満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>帯広市</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>第三期帯広市環境基本計画</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="inlineStr">
+        <is>
+          <t>令和2年度(2020)</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I20" s="30" t="inlineStr">
+        <is>
+          <t>一部確認（策定年のみ）</t>
+        </is>
+      </c>
+      <c r="J20" s="30" t="inlineStr">
+        <is>
+          <t>帯広市 第三期環境基本計画（令和2年3月策定）。第二期は平成22年度〜平成31年度。終期はPDF確認が必要</t>
+        </is>
+      </c>
+      <c r="K20" s="30" t="inlineStr">
+        <is>
+          <t>計画PDFで終期を確認する。10年計画なら令和11年度満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>北広島市</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>第3次北広島市環境基本計画</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
+      <c r="H21" s="31" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I21" s="31" t="inlineStr">
+        <is>
+          <t>一部確認（策定年・一部改定確認）</t>
+        </is>
+      </c>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>北広島市 第3次環境基本計画。第2次が令和2年度で10年の期間を終了。令和5年2月のゼロカーボンシティ宣言を受け、令和5年4月に地球環境分野を一部改定</t>
+        </is>
+      </c>
+      <c r="K21" s="31" t="inlineStr">
+        <is>
+          <t>計画PDFで終期を確認する。地球環境分野の一部改定実績があるため、国の2035年度目標を踏まえた再度の部分改定の余地もある</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>北見市</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>第2次北見市環境基本計画（改定版）</t>
+        </is>
+      </c>
+      <c r="G22" s="30" t="inlineStr">
+        <is>
+          <t>（未確認）</t>
+        </is>
+      </c>
+      <c r="H22" s="30" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I22" s="30" t="inlineStr">
+        <is>
+          <t>一部確認（計画掲載確認）</t>
+        </is>
+      </c>
+      <c r="J22" s="30" t="inlineStr">
+        <is>
+          <t>北見市 第2次環境基本計画（改定版）の掲載を確認。計画期間はHTML上で読めず、PDF確認が必要</t>
+        </is>
+      </c>
+      <c r="K22" s="30" t="inlineStr">
+        <is>
+          <t>計画PDFで計画期間を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>大崎市</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>第2次大崎市環境基本計画</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>令和2年度(2020)</t>
+        </is>
+      </c>
+      <c r="H23" s="31" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I23" s="31" t="inlineStr">
+        <is>
+          <t>一部確認（策定年のみ）</t>
+        </is>
+      </c>
+      <c r="J23" s="31" t="inlineStr">
+        <is>
+          <t>大崎市 第2次環境基本計画（令和2年3月策定・10年後を見据えた計画）。アクションプランも別途あり。終期はPDF確認が必要</t>
+        </is>
+      </c>
+      <c r="K23" s="31" t="inlineStr">
+        <is>
+          <t>計画PDFで終期を確認する。10年計画なら令和11年度満了</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>山形県</t>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>鶴岡市</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>一部確認</t>
+        </is>
+      </c>
+      <c r="F24" s="30" t="inlineStr">
+        <is>
+          <t>第2次鶴岡市環境基本計画</t>
+        </is>
+      </c>
+      <c r="G24" s="30" t="inlineStr">
+        <is>
+          <t>（未確認）</t>
+        </is>
+      </c>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I24" s="30" t="inlineStr">
+        <is>
+          <t>一部確認（計画掲載確認）</t>
+        </is>
+      </c>
+      <c r="J24" s="30" t="inlineStr">
+        <is>
+          <t>鶴岡市 第2次環境基本計画の掲載を確認。計画期間はHTML上で読めず、PDF確認が必要</t>
+        </is>
+      </c>
+      <c r="K24" s="30" t="inlineStr">
+        <is>
+          <t>計画PDFで計画期間を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>■ 環境基本計画そのものを確認できなかった先（未策定の可能性を含む）</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>計画未確認</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>青森市</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>義務</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="F26" s="30" t="inlineStr">
+        <is>
+          <t>環境基本計画は確認できず（関連：地球温暖化対策実行計画）</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="inlineStr">
+        <is>
+          <t>（未確認）</t>
+        </is>
+      </c>
+      <c r="H26" s="30" t="inlineStr">
+        <is>
+          <t>要確認（環境基本計画の有無から）</t>
+        </is>
+      </c>
+      <c r="I26" s="30" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="J26" s="30" t="inlineStr">
+        <is>
+          <t>青森市サイト・検索では環境基本計画を確認できず。地球温暖化対策実行計画（区域施策編 令和7年3月改定／事務事業編 第4期）は確認できる。中核市のため区域施策編は策定義務</t>
+        </is>
+      </c>
+      <c r="K26" s="30" t="inlineStr">
+        <is>
+          <t>環境基本計画の有無そのものを確認する。未策定なら新規策定提案の対象。策定済みなら計画名が異なる可能性があるため計画一覧から探す</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>計画未確認</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>十和田市</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>環境基本計画は確認できず（関連：環境保全率先行動計画・地球温暖化対策実行計画）</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="inlineStr">
+        <is>
+          <t>（未確認）</t>
+        </is>
+      </c>
+      <c r="H27" s="31" t="inlineStr">
+        <is>
+          <t>要確認（環境基本計画の有無から）</t>
+        </is>
+      </c>
+      <c r="I27" s="31" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="J27" s="31" t="inlineStr">
+        <is>
+          <t>十和田市サイト・検索では環境基本計画を確認できず。環境保全率先行動計画『とわだエコ・オフィスプラン』第5次が令和4年4月から令和8年度、地球温暖化対策実行計画（区域施策編）は確認できる</t>
+        </is>
+      </c>
+      <c r="K27" s="31" t="inlineStr">
+        <is>
+          <t>環境保全率先行動計画が令和8年度で満了するため、その改定を入口に環境基本計画の有無を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>計画未確認</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>小樽市</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>（確認できず）</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>（未確認）</t>
+        </is>
+      </c>
+      <c r="H28" s="30" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="I28" s="30" t="inlineStr">
+        <is>
+          <t>公式検索確認</t>
+        </is>
+      </c>
+      <c r="J28" s="30" t="inlineStr">
+        <is>
+          <t>小樽市サイト・検索では環境基本計画の計画期間を確認できず。『小樽市の環境』（年次報告）と緑の基本計画は確認できる</t>
+        </is>
+      </c>
+      <c r="K28" s="30" t="inlineStr">
+        <is>
+          <t>公式の計画一覧・生活環境部のページで環境基本計画の有無とPDFを継続確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>調査方法: 自治体サイトへの直接アクセスができない環境のため、公開情報の検索で確認できた範囲に限る。計画期間がHTML上に出ておらずPDF本文にしか記載がない団体が多く、そこは『一部確認』として終期欄を空欄のままにしている。</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="n"/>
+      <c r="C29" s="33" t="n"/>
+      <c r="D29" s="33" t="n"/>
+      <c r="E29" s="33" t="n"/>
+      <c r="F29" s="33" t="n"/>
+      <c r="G29" s="33" t="n"/>
+      <c r="H29" s="33" t="n"/>
+      <c r="I29" s="33" t="n"/>
+      <c r="J29" s="33" t="n"/>
+      <c r="K29" s="33" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>この調査で令和9年度末満了の新規該当先は出なかった。一方、令和8年度末満了（一関市＝今年度が改定年度）と、満了済・満了期（福島市・江別市）という、R9満了より先に動く先が3件見つかった。</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="n"/>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="33" t="n"/>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="33" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:K28"/>
+  <mergeCells count="6">
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/env_plan_sales_list_hokkaido_tohoku.xlsx
+++ b/output/env_plan_sales_list_hokkaido_tohoku.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="00_概要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_R9満了候補" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_営業先マスタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_確認手順" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_アプローチ設計" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_更新メモ" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_町村改訂時期_20260825" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_提出仕様_文字コード" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_改定時期調査_20260825b" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_概要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_R9満了候補" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_営業先マスタ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_確認手順" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_アプローチ設計" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_更新メモ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_町村改訂時期_20260825" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_提出仕様_文字コード" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_改定時期調査_20260825b" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_PDF確認待ち一覧" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_R9満了候補'!$A$2:$K$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_提出仕様_文字コード'!$A$2:$D$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_改定時期調査_20260825b'!$A$2:$K$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_PDF確認待ち一覧'!$A$2:$H$30</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -287,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -348,6 +350,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -1069,7 +1074,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -1201,6 +1205,1116 @@
     <mergeCell ref="A21:D21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>⑨ PDF確認待ち一覧 ｜ 検索では確定できない18件。PDFの計画期間1行で片付く</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="n"/>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="26" t="n"/>
+      <c r="E1" s="26" t="n"/>
+      <c r="F1" s="26" t="n"/>
+      <c r="G1" s="26" t="n"/>
+      <c r="H1" s="26" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="C2" s="27" t="inlineStr">
+        <is>
+          <t>自治体</t>
+        </is>
+      </c>
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>義務区分</t>
+        </is>
+      </c>
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>現在の状況</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
+        <is>
+          <t>計画掲載ページ</t>
+        </is>
+      </c>
+      <c r="G2" s="27" t="inlineStr">
+        <is>
+          <t>PDFで見る場所</t>
+        </is>
+      </c>
+      <c r="H2" s="27" t="inlineStr">
+        <is>
+          <t>確定したら入れる列</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="38" t="inlineStr">
+        <is>
+          <t>■ 対象18件（優先度順）。掲載ページを開き、PDFの計画期間の1行だけ確認する</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="n"/>
+      <c r="C3" s="29" t="n"/>
+      <c r="D3" s="29" t="n"/>
+      <c r="E3" s="29" t="n"/>
+      <c r="F3" s="29" t="n"/>
+      <c r="G3" s="29" t="n"/>
+      <c r="H3" s="29" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>函館市</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>義務（中核市）</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>環境基本計画［第3次計画］ 令和2年3月策定・終期未確認（中核市）</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>https://www.city.hakodate.hokkaido.jp/docs/2020033100148/</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>青森市</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>義務（中核市）</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>環境基本計画の有無から要確認（中核市）。計画一覧から探す</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>https://www.city.aomori.aomori.jp/shisei/machizukuri/1005734/</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>優先</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>義務（道）</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>北海道環境基本計画［第3次計画］ 令和3年3月策定・終期未確認</t>
+        </is>
+      </c>
+      <c r="F6" s="30" t="inlineStr">
+        <is>
+          <t>https://www.pref.hokkaido.lg.jp/ks/ksk/kihonkeikaku.html</t>
+        </is>
+      </c>
+      <c r="G6" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>優先</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>義務（県）</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>第3次秋田県環境基本計画 令和3年3月策定・終期未確認</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>https://www.pref.akita.lg.jp/pages/genre/13255</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>優先</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>義務（県）</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>福島県環境基本計画（第5次）・終期未確認</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>https://www.pref.fukushima.lg.jp/sec/16005a/5th-kankyoukihonkeikaku.html</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>帯広市</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>第三期帯広市環境基本計画 令和2年3月策定・終期未確認</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>https://www.city.obihiro.hokkaido.jp/kurashi/kankyo/kankobutsu/1003775.html</t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>北広島市</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>第3次北広島市環境基本計画 令和3年度〜・終期未確認</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>https://www.city.kitahiroshima.hokkaido.jp/hotnews/detail/00140680.html</t>
+        </is>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>北見市</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>第2次北見市環境基本計画（改定版）・期間未確認</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>https://www.city.kitami.lg.jp/detail.php?content=4642</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>大崎市</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>第2次大崎市環境基本計画 令和2年3月策定・終期未確認</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>https://www.city.osaki.miyagi.jp/shisei/soshikikarasagasu/shiminkyodousuishimbu/kankyohozenka/3/3329.html</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>山形県</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>鶴岡市</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>第2次鶴岡市環境基本計画・期間未確認</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>https://www.city.tsuruoka.lg.jp/seibi/kankyo/kihonkeikaku/dainizi_kankyoukihon.html</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>小樽市</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>環境基本計画の有無・期間とも未確認。計画一覧から探す</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="inlineStr">
+        <is>
+          <t>https://www.city.otaru.lg.jp/categories/bunya/keikaku/</t>
+        </is>
+      </c>
+      <c r="G14" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>十和田市</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>環境基本計画の有無から要確認。各種計画等一覧から探す</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>https://www.city.towada.lg.jp/shisei/other/2024-1220-1521-66.html</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H15" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>上士幌町</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>第2次上士幌町環境基本計画 令和6年度策定・終期未確認</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>https://www.kamishihoro.jp/page/00000416</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>新得町</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>環境基本計画・温対・適応計画の一体掲載・期間未確認</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>https://www.shintoku-town.jp/gyousei/koukai_kouhyou/tyoumin/kankyoukihonkeikaku/</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>池田町</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>池田町環境基本計画（第3次改訂）令和8年度改訂・終期未確認</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>https://www.town.hokkaido-ikeda.lg.jp/kurashi/kankyo/430.html</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>厚岸町</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>第2期厚岸町豊かな環境を守り育てる基本計画・期間未確認</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>https://www.akkeshi-town.jp/gyosei/seisaku/kankyo/kankyo19/</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>鶴居村</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>第2次鶴居村環境基本計画・期間未確認</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>https://www.vill.tsurui.lg.jp/soshikikarasagasu/kikakuzaiseika/muranokeikaku/804.html</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>弟子屈町</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>努力義務</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>外部DBで計画名のみ確認。公式ページ・期間とも未確認</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>https://www.town.teshikaga.hokkaido.jp/</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>表紙／第1章『計画の期間』。多くは「計画期間は、○年度から○年度までの○年間」の1行</t>
+        </is>
+      </c>
+      <c r="H21" s="31" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>■ 手順（制限のない環境で実行する）</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="29" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>手順1</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr"/>
+      <c r="C23" s="31" t="inlineStr"/>
+      <c r="D23" s="31" t="inlineStr"/>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>計画ページからPDFを一括取得する</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>python3 fetch_plan_pdfs.py --out plan_pdfs</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>手順2</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr"/>
+      <c r="C24" s="30" t="inlineStr"/>
+      <c r="D24" s="30" t="inlineStr"/>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>PDF→Word変換のうえ計画期間を一括抽出する</t>
+        </is>
+      </c>
+      <c r="F24" s="30" t="inlineStr">
+        <is>
+          <t>python3 batch_extract_plan_periods.py plan_pdfs</t>
+        </is>
+      </c>
+      <c r="G24" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>計画期間抽出結果.csv が出る</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>手順3</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr"/>
+      <c r="C25" s="31" t="inlineStr"/>
+      <c r="D25" s="31" t="inlineStr"/>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>1件だけ確認する場合</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>python3 extract_plan_period.py &lt;PDFパス&gt;</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>手順4</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr"/>
+      <c r="C26" s="30" t="inlineStr"/>
+      <c r="D26" s="30" t="inlineStr"/>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>抽出結果を02_営業先マスタへ転記し、終期がR9(2027)の先を01_R9満了候補へ移す</t>
+        </is>
+      </c>
+      <c r="F26" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="30" t="inlineStr">
+        <is>
+          <t>02_営業先マスタ H列(開始)・I列(終期)・J列(判定)・K列(確認状況)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="38" t="inlineStr">
+        <is>
+          <t>■ 補足</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="29" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr"/>
+      <c r="C28" s="30" t="inlineStr"/>
+      <c r="D28" s="30" t="inlineStr"/>
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>自動取得に失敗する団体は、掲載ページを開いてPDFを手で保存し、ファイル名の先頭を自治体名にして同じフォルダへ置けば手順2で処理できる</t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>例: 函館市_環境基本計画.pdf</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="inlineStr"/>
+      <c r="C29" s="31" t="inlineStr"/>
+      <c r="D29" s="31" t="inlineStr"/>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>画像のみのスキャンPDFはOCRが必要。抽出ツールはその旨を表示して中断する</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr"/>
+      <c r="C30" s="30" t="inlineStr"/>
+      <c r="D30" s="30" t="inlineStr"/>
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>抽出はスコア付きで候補を出す。スコアが低い場合は根拠行を目視で確認してから確定させる</t>
+        </is>
+      </c>
+      <c r="F30" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>本シートを作った理由: 第2回調査（08シート）で公開情報の検索から確認できる先は確認しきった。残る18件は計画期間がPDF本文にしかなく、検索の要約に出てこないため検索経路では確定できない。加えて本作業環境は全ホストへのアウトバウンド接続が組織のegressポリシーで遮断されており（CONNECTに403）、PDFを取得できない。</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="n"/>
+      <c r="C31" s="33" t="n"/>
+      <c r="D31" s="33" t="n"/>
+      <c r="E31" s="33" t="n"/>
+      <c r="F31" s="33" t="n"/>
+      <c r="G31" s="33" t="n"/>
+      <c r="H31" s="33" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:H30"/>
+  <mergeCells count="5">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A22:H22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -29088,7 +30202,6 @@
       </c>
       <c r="O415" s="4" t="inlineStr"/>
     </row>
-    <row r="416"/>
     <row r="417">
       <c r="A417" s="6" t="inlineStr">
         <is>
@@ -30166,7 +31279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.5" customWidth="1" min="1" max="1"/>
@@ -30533,6 +31646,33 @@
       <c r="E16" s="16" t="inlineStr">
         <is>
           <t>08_改定時期調査_20260825b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-25 PDF確認待ち</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>未確認先18件</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>検索で確定できる先は第2回で確認しきったため、残りをPDF確認待ちとして09シートに整理。取得スクリプトと一括抽出ツールを用意</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>制限のない環境でPDFを取得すれば1コマンドで確定できる。函館市・青森市（いずれも中核市）が最優先</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>09_PDF確認待ち一覧 ／ fetch_plan_pdfs.py ／ batch_extract_plan_periods.py</t>
         </is>
       </c>
     </row>
@@ -33409,16 +34549,6 @@
           <t>⑧ 改定時期調査（2026-08-25 第2回）｜ 義務団体・主要市の未確認先を優先に確認</t>
         </is>
       </c>
-      <c r="B1" s="26" t="n"/>
-      <c r="C1" s="26" t="n"/>
-      <c r="D1" s="26" t="n"/>
-      <c r="E1" s="26" t="n"/>
-      <c r="F1" s="26" t="n"/>
-      <c r="G1" s="26" t="n"/>
-      <c r="H1" s="26" t="n"/>
-      <c r="I1" s="26" t="n"/>
-      <c r="J1" s="26" t="n"/>
-      <c r="K1" s="26" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
@@ -33483,16 +34613,16 @@
           <t>■ 終期を特定できた先（確認済）</t>
         </is>
       </c>
-      <c r="B3" s="29" t="n"/>
-      <c r="C3" s="29" t="n"/>
-      <c r="D3" s="29" t="n"/>
-      <c r="E3" s="29" t="n"/>
-      <c r="F3" s="29" t="n"/>
-      <c r="G3" s="29" t="n"/>
-      <c r="H3" s="29" t="n"/>
-      <c r="I3" s="29" t="n"/>
-      <c r="J3" s="29" t="n"/>
-      <c r="K3" s="29" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="36" t="n"/>
+      <c r="D3" s="36" t="n"/>
+      <c r="E3" s="36" t="n"/>
+      <c r="F3" s="36" t="n"/>
+      <c r="G3" s="36" t="n"/>
+      <c r="H3" s="36" t="n"/>
+      <c r="I3" s="36" t="n"/>
+      <c r="J3" s="36" t="n"/>
+      <c r="K3" s="37" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
@@ -34127,16 +35257,16 @@
           <t>■ 計画名・策定年のみ判明（終期は未確認のまま。推測で埋めない）</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n"/>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="29" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="29" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="37" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
@@ -34657,16 +35787,16 @@
           <t>■ 環境基本計画そのものを確認できなかった先（未策定の可能性を含む）</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="29" t="n"/>
-      <c r="F25" s="29" t="n"/>
-      <c r="G25" s="29" t="n"/>
-      <c r="H25" s="29" t="n"/>
-      <c r="I25" s="29" t="n"/>
-      <c r="J25" s="29" t="n"/>
-      <c r="K25" s="29" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
+      <c r="J25" s="36" t="n"/>
+      <c r="K25" s="37" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
@@ -34845,16 +35975,6 @@
           <t>調査方法: 自治体サイトへの直接アクセスができない環境のため、公開情報の検索で確認できた範囲に限る。計画期間がHTML上に出ておらずPDF本文にしか記載がない団体が多く、そこは『一部確認』として終期欄を空欄のままにしている。</t>
         </is>
       </c>
-      <c r="B29" s="33" t="n"/>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="33" t="n"/>
-      <c r="E29" s="33" t="n"/>
-      <c r="F29" s="33" t="n"/>
-      <c r="G29" s="33" t="n"/>
-      <c r="H29" s="33" t="n"/>
-      <c r="I29" s="33" t="n"/>
-      <c r="J29" s="33" t="n"/>
-      <c r="K29" s="33" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="32" t="inlineStr">
@@ -34862,16 +35982,6 @@
           <t>この調査で令和9年度末満了の新規該当先は出なかった。一方、令和8年度末満了（一関市＝今年度が改定年度）と、満了済・満了期（福島市・江別市）という、R9満了より先に動く先が3件見つかった。</t>
         </is>
       </c>
-      <c r="B30" s="33" t="n"/>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="33" t="n"/>
-      <c r="E30" s="33" t="n"/>
-      <c r="F30" s="33" t="n"/>
-      <c r="G30" s="33" t="n"/>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="33" t="n"/>
-      <c r="J30" s="33" t="n"/>
-      <c r="K30" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:K28"/>
